--- a/www/flightdata/xlsx/eoss-297.xlsx
+++ b/www/flightdata/xlsx/eoss-297.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="516">
   <si>
     <t>flight</t>
   </si>
@@ -36,6 +36,18 @@
     <t>h2fill</t>
   </si>
   <si>
+    <t>maxaltitude</t>
+  </si>
+  <si>
+    <t>numpoints</t>
+  </si>
+  <si>
+    <t>flighttime</t>
+  </si>
+  <si>
+    <t>flighttime_secs</t>
+  </si>
+  <si>
     <t>weights.client</t>
   </si>
   <si>
@@ -73,6 +85,9 @@
   </si>
   <si>
     <t>238</t>
+  </si>
+  <si>
+    <t>1hrs 57mins 35secs</t>
   </si>
   <si>
     <t>6.78</t>
@@ -1910,10 +1925,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1953,46 +1968,70 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>85332</v>
+      </c>
+      <c r="H2">
+        <v>224</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J2">
+        <v>7055</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2007,102 +2046,102 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2">
         <v>43905.35455440972</v>
@@ -2120,13 +2159,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K2">
         <v>193</v>
@@ -2150,7 +2189,7 @@
         <v>7.79310345</v>
       </c>
       <c r="V2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="X2">
         <v>7.793103</v>
@@ -2161,10 +2200,10 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2">
         <v>43905.35454506944</v>
@@ -2182,13 +2221,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="K3">
         <v>228</v>
@@ -2212,7 +2251,7 @@
         <v>19.63333333</v>
       </c>
       <c r="V3" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W3">
         <v>0.394674</v>
@@ -2235,10 +2274,10 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2">
         <v>43905.35493925926</v>
@@ -2256,13 +2295,13 @@
         <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="K4">
         <v>265</v>
@@ -2286,7 +2325,7 @@
         <v>21.72413793</v>
       </c>
       <c r="V4" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W4">
         <v>0.07209699999999999</v>
@@ -2315,10 +2354,10 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>43905.3548868287</v>
@@ -2336,13 +2375,13 @@
         <v>43</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J5" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="K5">
         <v>12</v>
@@ -2366,7 +2405,7 @@
         <v>20.23333333</v>
       </c>
       <c r="V5" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W5">
         <v>-0.049693</v>
@@ -2395,10 +2434,10 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2">
         <v>43905.35533289352</v>
@@ -2416,13 +2455,13 @@
         <v>58</v>
       </c>
       <c r="H6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J6" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="K6">
         <v>74</v>
@@ -2446,7 +2485,7 @@
         <v>21.72413793</v>
       </c>
       <c r="V6" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W6">
         <v>0.051407</v>
@@ -2475,10 +2514,10 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C7" s="2">
         <v>43905.35523523148</v>
@@ -2496,13 +2535,13 @@
         <v>73</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J7" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="K7">
         <v>311</v>
@@ -2526,7 +2565,7 @@
         <v>22.8</v>
       </c>
       <c r="V7" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W7">
         <v>0.035862</v>
@@ -2555,10 +2594,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2">
         <v>43905.35540681713</v>
@@ -2576,13 +2615,13 @@
         <v>87</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J8" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="K8">
         <v>352</v>
@@ -2606,7 +2645,7 @@
         <v>23.4137931</v>
       </c>
       <c r="V8" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W8">
         <v>0.021165</v>
@@ -2635,10 +2674,10 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C9" s="2">
         <v>43905.35558158565</v>
@@ -2656,13 +2695,13 @@
         <v>103</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J9" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -2686,7 +2725,7 @@
         <v>21.53333333</v>
       </c>
       <c r="V9" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W9">
         <v>-0.062682</v>
@@ -2715,10 +2754,10 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2">
         <v>43905.35580268518</v>
@@ -2736,13 +2775,13 @@
         <v>116</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J10" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="K10">
         <v>34</v>
@@ -2766,7 +2805,7 @@
         <v>20.93103448</v>
       </c>
       <c r="V10" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W10">
         <v>-0.020769</v>
@@ -2795,10 +2834,10 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C11" s="2">
         <v>43905.35592921296</v>
@@ -2816,13 +2855,13 @@
         <v>133</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J11" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="K11">
         <v>16</v>
@@ -2846,7 +2885,7 @@
         <v>20</v>
       </c>
       <c r="V11" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W11">
         <v>-0.031034</v>
@@ -2875,10 +2914,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C12" s="2">
         <v>43905.35619954861</v>
@@ -2896,13 +2935,13 @@
         <v>145</v>
       </c>
       <c r="H12" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J12" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="K12">
         <v>27</v>
@@ -2926,7 +2965,7 @@
         <v>20.03448276</v>
       </c>
       <c r="V12" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W12">
         <v>0.001189</v>
@@ -2955,10 +2994,10 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C13" s="2">
         <v>43905.35627532408</v>
@@ -2976,13 +3015,13 @@
         <v>163</v>
       </c>
       <c r="H13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J13" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -3006,7 +3045,7 @@
         <v>22.13333333</v>
       </c>
       <c r="V13" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W13">
         <v>0.069962</v>
@@ -3035,10 +3074,10 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2">
         <v>43905.35658402778</v>
@@ -3056,13 +3095,13 @@
         <v>174</v>
       </c>
       <c r="H14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J14" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="K14">
         <v>4</v>
@@ -3086,7 +3125,7 @@
         <v>21.51724138</v>
       </c>
       <c r="V14" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W14">
         <v>-0.021245</v>
@@ -3115,10 +3154,10 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C15" s="2">
         <v>43905.35662277778</v>
@@ -3136,13 +3175,13 @@
         <v>193</v>
       </c>
       <c r="H15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I15" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J15" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K15">
         <v>43</v>
@@ -3166,7 +3205,7 @@
         <v>20.23333333</v>
       </c>
       <c r="V15" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W15">
         <v>-0.042797</v>
@@ -3195,10 +3234,10 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C16" s="2">
         <v>43905.35698546296</v>
@@ -3216,13 +3255,13 @@
         <v>203</v>
       </c>
       <c r="H16" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J16" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K16">
         <v>353</v>
@@ -3246,7 +3285,7 @@
         <v>20.24137931</v>
       </c>
       <c r="V16" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W16">
         <v>0.000277</v>
@@ -3275,10 +3314,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C17" s="2">
         <v>43905.35697372686</v>
@@ -3296,13 +3335,13 @@
         <v>223</v>
       </c>
       <c r="H17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I17" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J17" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K17">
         <v>358</v>
@@ -3326,7 +3365,7 @@
         <v>20</v>
       </c>
       <c r="V17" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W17">
         <v>-0.008045999999999999</v>
@@ -3355,10 +3394,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C18" s="2">
         <v>43905.3573178125</v>
@@ -3376,13 +3415,13 @@
         <v>253</v>
       </c>
       <c r="H18" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I18" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J18" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="K18">
         <v>67</v>
@@ -3406,7 +3445,7 @@
         <v>18.76666667</v>
       </c>
       <c r="V18" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W18">
         <v>-0.041111</v>
@@ -3435,10 +3474,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2">
         <v>43905.35744141204</v>
@@ -3456,13 +3495,13 @@
         <v>261</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J19" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="K19">
         <v>7</v>
@@ -3486,7 +3525,7 @@
         <v>19.12068966</v>
       </c>
       <c r="V19" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W19">
         <v>0.006104</v>
@@ -3515,10 +3554,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2">
         <v>43905.35766472222</v>
@@ -3536,13 +3575,13 @@
         <v>283</v>
       </c>
       <c r="H20" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K20">
         <v>11</v>
@@ -3566,7 +3605,7 @@
         <v>19.36666667</v>
       </c>
       <c r="V20" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W20">
         <v>0.008199</v>
@@ -3595,10 +3634,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C21" s="2">
         <v>43905.35783949074</v>
@@ -3616,13 +3655,13 @@
         <v>290</v>
       </c>
       <c r="H21" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J21" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="K21">
         <v>32</v>
@@ -3646,7 +3685,7 @@
         <v>19.89655172</v>
       </c>
       <c r="V21" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W21">
         <v>0.018272</v>
@@ -3675,10 +3714,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C22" s="2">
         <v>43905.35801684028</v>
@@ -3696,13 +3735,13 @@
         <v>313</v>
       </c>
       <c r="H22" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I22" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J22" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K22">
         <v>349</v>
@@ -3726,7 +3765,7 @@
         <v>20</v>
       </c>
       <c r="V22" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W22">
         <v>0.003448</v>
@@ -3755,10 +3794,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C23" s="2">
         <v>43905.35822041667</v>
@@ -3776,13 +3815,13 @@
         <v>319</v>
       </c>
       <c r="H23" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I23" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J23" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K23">
         <v>38</v>
@@ -3806,7 +3845,7 @@
         <v>20.03448276</v>
       </c>
       <c r="V23" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W23">
         <v>0.001189</v>
@@ -3835,10 +3874,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C24" s="2">
         <v>43905.35835924769</v>
@@ -3856,13 +3895,13 @@
         <v>343</v>
       </c>
       <c r="H24" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J24" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K24">
         <v>333</v>
@@ -3886,7 +3925,7 @@
         <v>19.73333333</v>
       </c>
       <c r="V24" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W24">
         <v>-0.010038</v>
@@ -3915,10 +3954,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2">
         <v>43905.3586212037</v>
@@ -3936,13 +3975,13 @@
         <v>348</v>
       </c>
       <c r="H25" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I25" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J25" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="K25">
         <v>315</v>
@@ -3966,7 +4005,7 @@
         <v>19.48275862</v>
       </c>
       <c r="V25" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W25">
         <v>-0.008640999999999999</v>
@@ -3995,10 +4034,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2">
         <v>43905.35870618055</v>
@@ -4016,13 +4055,13 @@
         <v>373</v>
       </c>
       <c r="H26" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I26" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J26" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="K26">
         <v>10</v>
@@ -4046,7 +4085,7 @@
         <v>20.33333333</v>
       </c>
       <c r="V26" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W26">
         <v>0.028352</v>
@@ -4075,10 +4114,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C27" s="2">
         <v>43905.35901060185</v>
@@ -4096,13 +4135,13 @@
         <v>377</v>
       </c>
       <c r="H27" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I27" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J27" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K27">
         <v>33</v>
@@ -4126,7 +4165,7 @@
         <v>20.93103448</v>
       </c>
       <c r="V27" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W27">
         <v>0.02061</v>
@@ -4155,10 +4194,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2">
         <v>43905.35905450232</v>
@@ -4176,13 +4215,13 @@
         <v>403</v>
       </c>
       <c r="H28" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J28" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K28">
         <v>2</v>
@@ -4206,7 +4245,7 @@
         <v>21.13333333</v>
       </c>
       <c r="V28" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W28">
         <v>0.006743</v>
@@ -4235,10 +4274,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C29" s="2">
         <v>43905.35940105324</v>
@@ -4256,13 +4295,13 @@
         <v>433</v>
       </c>
       <c r="H29" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I29" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J29" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K29">
         <v>42</v>
@@ -4286,7 +4325,7 @@
         <v>20.26666667</v>
       </c>
       <c r="V29" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W29">
         <v>-0.028889</v>
@@ -4315,10 +4354,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2">
         <v>43905.35946864583</v>
@@ -4336,13 +4375,13 @@
         <v>435</v>
       </c>
       <c r="H30" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I30" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J30" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="K30">
         <v>48</v>
@@ -4366,7 +4405,7 @@
         <v>20.75862069</v>
       </c>
       <c r="V30" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W30">
         <v>0.008482</v>
@@ -4395,10 +4434,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2">
         <v>43905.35974765047</v>
@@ -4416,13 +4455,13 @@
         <v>463</v>
       </c>
       <c r="H31" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I31" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J31" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K31">
         <v>67</v>
@@ -4446,7 +4485,7 @@
         <v>23.03333333</v>
       </c>
       <c r="V31" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W31">
         <v>0.075824</v>
@@ -4475,10 +4514,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C32" s="2">
         <v>43905.36009555555</v>
@@ -4496,13 +4535,13 @@
         <v>493</v>
       </c>
       <c r="H32" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I32" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J32" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K32">
         <v>59</v>
@@ -4526,7 +4565,7 @@
         <v>21.7</v>
       </c>
       <c r="V32" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W32">
         <v>-0.044444</v>
@@ -4555,10 +4594,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C33" s="2">
         <v>43905.36025887731</v>
@@ -4576,13 +4615,13 @@
         <v>493</v>
       </c>
       <c r="H33" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I33" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J33" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K33">
         <v>65</v>
@@ -4606,7 +4645,7 @@
         <v>22.39655172</v>
       </c>
       <c r="V33" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W33">
         <v>0.01201</v>
@@ -4635,10 +4674,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C34" s="2">
         <v>43905.36064675926</v>
@@ -4656,13 +4695,13 @@
         <v>522</v>
       </c>
       <c r="H34" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I34" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J34" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K34">
         <v>72</v>
@@ -4686,7 +4725,7 @@
         <v>18.68965517</v>
       </c>
       <c r="V34" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W34">
         <v>-0.127824</v>
@@ -4715,10 +4754,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C35" s="2">
         <v>43905.36044202546</v>
@@ -4736,13 +4775,13 @@
         <v>523</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I35" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J35" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K35">
         <v>62</v>
@@ -4766,7 +4805,7 @@
         <v>19</v>
       </c>
       <c r="V35" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W35">
         <v>0.010345</v>
@@ -4795,10 +4834,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C36" s="2">
         <v>43905.36079018519</v>
@@ -4816,13 +4855,13 @@
         <v>553</v>
       </c>
       <c r="H36" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I36" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J36" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K36">
         <v>64</v>
@@ -4846,7 +4885,7 @@
         <v>18.8</v>
       </c>
       <c r="V36" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W36">
         <v>-0.006667</v>
@@ -4875,10 +4914,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C37" s="2">
         <v>43905.36111953704</v>
@@ -4896,13 +4935,13 @@
         <v>580</v>
       </c>
       <c r="H37" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I37" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J37" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="K37">
         <v>78</v>
@@ -4926,7 +4965,7 @@
         <v>19.84482759</v>
       </c>
       <c r="V37" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W37">
         <v>0.018014</v>
@@ -4955,10 +4994,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C38" s="2">
         <v>43905.36113657407</v>
@@ -4976,13 +5015,13 @@
         <v>583</v>
       </c>
       <c r="H38" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I38" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J38" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K38">
         <v>61</v>
@@ -5006,7 +5045,7 @@
         <v>21.1</v>
       </c>
       <c r="V38" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W38">
         <v>0.041839</v>
@@ -5035,10 +5074,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C39" s="2">
         <v>43905.36150556713</v>
@@ -5056,13 +5095,13 @@
         <v>609</v>
       </c>
       <c r="H39" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I39" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J39" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K39">
         <v>46</v>
@@ -5086,7 +5125,7 @@
         <v>21.96551724</v>
       </c>
       <c r="V39" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W39">
         <v>0.029845</v>
@@ -5115,10 +5154,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C40" s="2">
         <v>43905.36148440972</v>
@@ -5136,13 +5175,13 @@
         <v>613</v>
       </c>
       <c r="H40" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I40" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J40" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="K40">
         <v>64</v>
@@ -5166,7 +5205,7 @@
         <v>21.73333333</v>
       </c>
       <c r="V40" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W40">
         <v>-0.007739</v>
@@ -5195,10 +5234,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C41" s="2">
         <v>43905.36190732639</v>
@@ -5216,13 +5255,13 @@
         <v>638</v>
       </c>
       <c r="H41" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I41" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J41" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="K41">
         <v>64</v>
@@ -5246,7 +5285,7 @@
         <v>18.65517241</v>
       </c>
       <c r="V41" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W41">
         <v>-0.106143</v>
@@ -5275,10 +5314,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C42" s="2">
         <v>43905.36183105324</v>
@@ -5296,13 +5335,13 @@
         <v>643</v>
       </c>
       <c r="H42" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I42" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J42" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="K42">
         <v>48</v>
@@ -5326,7 +5365,7 @@
         <v>18.8</v>
       </c>
       <c r="V42" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W42">
         <v>0.004828</v>
@@ -5355,10 +5394,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C43" s="2">
         <v>43905.3623027662</v>
@@ -5376,13 +5415,13 @@
         <v>667</v>
       </c>
       <c r="H43" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I43" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="J43" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K43">
         <v>47</v>
@@ -5406,7 +5445,7 @@
         <v>18.44827586</v>
       </c>
       <c r="V43" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W43">
         <v>-0.012128</v>
@@ -5435,10 +5474,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C44" s="2">
         <v>43905.36217925926</v>
@@ -5456,13 +5495,13 @@
         <v>673</v>
       </c>
       <c r="H44" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I44" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J44" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K44">
         <v>52</v>
@@ -5486,7 +5525,7 @@
         <v>18.03333333</v>
       </c>
       <c r="V44" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W44">
         <v>-0.013831</v>
@@ -5515,10 +5554,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C45" s="2">
         <v>43905.36270061343</v>
@@ -5536,13 +5575,13 @@
         <v>696</v>
       </c>
       <c r="H45" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I45" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J45" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K45">
         <v>52</v>
@@ -5566,7 +5605,7 @@
         <v>18.20689655</v>
       </c>
       <c r="V45" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W45">
         <v>0.005985</v>
@@ -5595,10 +5634,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C46" s="2">
         <v>43905.36252603009</v>
@@ -5616,13 +5655,13 @@
         <v>703</v>
       </c>
       <c r="H46" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I46" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J46" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K46">
         <v>44</v>
@@ -5646,7 +5685,7 @@
         <v>18.4</v>
       </c>
       <c r="V46" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W46">
         <v>0.006437</v>
@@ -5675,10 +5714,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C47" s="2">
         <v>43905.36287436343</v>
@@ -5696,13 +5735,13 @@
         <v>733</v>
       </c>
       <c r="H47" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I47" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J47" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="K47">
         <v>68</v>
@@ -5726,7 +5765,7 @@
         <v>21.83333333</v>
       </c>
       <c r="V47" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W47">
         <v>0.114444</v>
@@ -5755,10 +5794,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C48" s="2">
         <v>43905.36314751158</v>
@@ -5776,13 +5815,13 @@
         <v>754</v>
       </c>
       <c r="H48" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I48" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J48" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K48">
         <v>79</v>
@@ -5806,7 +5845,7 @@
         <v>21.17241379</v>
       </c>
       <c r="V48" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W48">
         <v>-0.011395</v>
@@ -5835,10 +5874,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C49" s="2">
         <v>43905.36322112269</v>
@@ -5856,13 +5895,13 @@
         <v>763</v>
       </c>
       <c r="H49" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I49" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J49" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="K49">
         <v>68</v>
@@ -5886,7 +5925,7 @@
         <v>18.4</v>
       </c>
       <c r="V49" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W49">
         <v>-0.092414</v>
@@ -5915,10 +5954,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C50" s="2">
         <v>43905.36354105324</v>
@@ -5936,13 +5975,13 @@
         <v>783</v>
       </c>
       <c r="H50" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I50" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J50" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K50">
         <v>84</v>
@@ -5966,7 +6005,7 @@
         <v>20.13793103</v>
       </c>
       <c r="V50" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W50">
         <v>0.059929</v>
@@ -5995,10 +6034,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C51" s="2">
         <v>43905.36356884259</v>
@@ -6016,13 +6055,13 @@
         <v>793</v>
       </c>
       <c r="H51" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I51" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J51" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K51">
         <v>75</v>
@@ -6046,7 +6085,7 @@
         <v>22.33333333</v>
       </c>
       <c r="V51" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W51">
         <v>0.07318</v>
@@ -6075,10 +6114,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C52" s="2">
         <v>43905.36394129629</v>
@@ -6096,13 +6135,13 @@
         <v>812</v>
       </c>
       <c r="H52" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I52" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J52" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K52">
         <v>72</v>
@@ -6126,7 +6165,7 @@
         <v>21.72413793</v>
       </c>
       <c r="V52" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W52">
         <v>-0.021007</v>
@@ -6155,10 +6194,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C53" s="2">
         <v>43905.36391539352</v>
@@ -6176,13 +6215,13 @@
         <v>823</v>
       </c>
       <c r="H53" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I53" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="J53" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="K53">
         <v>66</v>
@@ -6206,7 +6245,7 @@
         <v>21.73333333</v>
       </c>
       <c r="V53" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W53">
         <v>0.000307</v>
@@ -6235,10 +6274,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C54" s="2">
         <v>43905.36433449074</v>
@@ -6256,13 +6295,13 @@
         <v>841</v>
       </c>
       <c r="H54" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I54" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="J54" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="K54">
         <v>62</v>
@@ -6286,7 +6325,7 @@
         <v>21.27586207</v>
       </c>
       <c r="V54" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W54">
         <v>-0.015775</v>
@@ -6315,10 +6354,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C55" s="2">
         <v>43905.36426375</v>
@@ -6336,13 +6375,13 @@
         <v>853</v>
       </c>
       <c r="H55" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I55" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J55" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="K55">
         <v>65</v>
@@ -6366,7 +6405,7 @@
         <v>21.03333333</v>
       </c>
       <c r="V55" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W55">
         <v>-0.008083999999999999</v>
@@ -6395,10 +6434,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C56" s="2">
         <v>43905.36460951389</v>
@@ -6416,13 +6455,13 @@
         <v>883</v>
       </c>
       <c r="H56" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I56" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J56" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="K56">
         <v>82</v>
@@ -6446,7 +6485,7 @@
         <v>25.2</v>
       </c>
       <c r="V56" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W56">
         <v>0.138889</v>
@@ -6475,10 +6514,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C57" s="2">
         <v>43905.36495675926</v>
@@ -6496,13 +6535,13 @@
         <v>913</v>
       </c>
       <c r="H57" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I57" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J57" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K57">
         <v>77</v>
@@ -6526,7 +6565,7 @@
         <v>21.8</v>
       </c>
       <c r="V57" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W57">
         <v>-0.113333</v>
@@ -6555,10 +6594,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C58" s="2">
         <v>43905.36518355324</v>
@@ -6576,13 +6615,13 @@
         <v>928</v>
       </c>
       <c r="H58" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I58" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J58" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="K58">
         <v>69</v>
@@ -6606,7 +6645,7 @@
         <v>22.81609195</v>
       </c>
       <c r="V58" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W58">
         <v>0.011679</v>
@@ -6635,10 +6674,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C59" s="2">
         <v>43905.36530372685</v>
@@ -6656,13 +6695,13 @@
         <v>943</v>
       </c>
       <c r="H59" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I59" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J59" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="K59">
         <v>65</v>
@@ -6686,7 +6725,7 @@
         <v>22.63333333</v>
       </c>
       <c r="V59" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W59">
         <v>-0.006092</v>
@@ -6715,10 +6754,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C60" s="2">
         <v>43905.36558168982</v>
@@ -6736,13 +6775,13 @@
         <v>957</v>
       </c>
       <c r="H60" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I60" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J60" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="K60">
         <v>75</v>
@@ -6766,7 +6805,7 @@
         <v>23.06896552</v>
       </c>
       <c r="V60" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W60">
         <v>0.015022</v>
@@ -6795,10 +6834,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C61" s="2">
         <v>43905.36565145833</v>
@@ -6816,13 +6855,13 @@
         <v>973</v>
       </c>
       <c r="H61" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I61" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="J61" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K61">
         <v>69</v>
@@ -6846,7 +6885,7 @@
         <v>22.33333333</v>
       </c>
       <c r="V61" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W61">
         <v>-0.024521</v>
@@ -6875,10 +6914,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C62" s="2">
         <v>43905.36597920139</v>
@@ -6896,13 +6935,13 @@
         <v>986</v>
       </c>
       <c r="H62" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I62" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J62" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="K62">
         <v>71</v>
@@ -6926,7 +6965,7 @@
         <v>22.17241379</v>
       </c>
       <c r="V62" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W62">
         <v>-0.005549</v>
@@ -6955,10 +6994,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C63" s="2">
         <v>43905.36600150463</v>
@@ -6976,13 +7015,13 @@
         <v>1003</v>
       </c>
       <c r="H63" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I63" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="J63" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K63">
         <v>64</v>
@@ -7006,7 +7045,7 @@
         <v>24.73333333</v>
       </c>
       <c r="V63" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W63">
         <v>0.085364</v>
@@ -7035,10 +7074,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C64" s="2">
         <v>43905.3663808912</v>
@@ -7056,13 +7095,13 @@
         <v>1015</v>
       </c>
       <c r="H64" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I64" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J64" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="K64">
         <v>61</v>
@@ -7086,7 +7125,7 @@
         <v>22.65517241</v>
       </c>
       <c r="V64" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W64">
         <v>-0.071661</v>
@@ -7115,10 +7154,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C65" s="2">
         <v>43905.36634446759</v>
@@ -7136,13 +7175,13 @@
         <v>1033</v>
       </c>
       <c r="H65" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I65" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J65" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K65">
         <v>64</v>
@@ -7166,7 +7205,7 @@
         <v>18.06666667</v>
       </c>
       <c r="V65" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W65">
         <v>-0.15295</v>
@@ -7195,10 +7234,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C66" s="2">
         <v>43905.36669266204</v>
@@ -7216,13 +7255,13 @@
         <v>1063</v>
       </c>
       <c r="H66" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I66" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J66" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K66">
         <v>76</v>
@@ -7246,7 +7285,7 @@
         <v>19.26666667</v>
       </c>
       <c r="V66" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W66">
         <v>0.04</v>
@@ -7275,10 +7314,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C67" s="2">
         <v>43905.36685060185</v>
@@ -7296,13 +7335,13 @@
         <v>1073</v>
       </c>
       <c r="H67" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I67" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J67" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="K67">
         <v>70</v>
@@ -7326,7 +7365,7 @@
         <v>20.98275862</v>
       </c>
       <c r="V67" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W67">
         <v>0.029588</v>
@@ -7355,10 +7394,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C68" s="2">
         <v>43905.36704002315</v>
@@ -7376,13 +7415,13 @@
         <v>1093</v>
       </c>
       <c r="H68" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I68" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J68" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="K68">
         <v>58</v>
@@ -7406,7 +7445,7 @@
         <v>25.8</v>
       </c>
       <c r="V68" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W68">
         <v>0.160575</v>
@@ -7435,10 +7474,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C69" s="2">
         <v>43905.36726461806</v>
@@ -7456,13 +7495,13 @@
         <v>1102</v>
       </c>
       <c r="H69" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I69" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J69" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K69">
         <v>70</v>
@@ -7486,7 +7525,7 @@
         <v>24.75862069</v>
       </c>
       <c r="V69" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W69">
         <v>-0.03591</v>
@@ -7515,10 +7554,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C70" s="2">
         <v>43905.36767171296</v>
@@ -7536,13 +7575,13 @@
         <v>1131</v>
       </c>
       <c r="H70" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I70" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J70" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="K70">
         <v>76</v>
@@ -7566,7 +7605,7 @@
         <v>24.24137931</v>
       </c>
       <c r="V70" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W70">
         <v>-0.017836</v>
@@ -7595,10 +7634,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C71" s="2">
         <v>43905.36773390046</v>
@@ -7616,13 +7655,13 @@
         <v>1153</v>
       </c>
       <c r="H71" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I71" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J71" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K71">
         <v>67</v>
@@ -7646,7 +7685,7 @@
         <v>19.21666667</v>
       </c>
       <c r="V71" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W71">
         <v>-0.083745</v>
@@ -7675,10 +7714,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C72" s="2">
         <v>43905.36895555555</v>
@@ -7696,13 +7735,13 @@
         <v>1247</v>
       </c>
       <c r="H72" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I72" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J72" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K72">
         <v>66</v>
@@ -7726,7 +7765,7 @@
         <v>21.26724138</v>
       </c>
       <c r="V72" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W72">
         <v>0.017677</v>
@@ -7755,10 +7794,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C73" s="2">
         <v>43905.36935763889</v>
@@ -7776,13 +7815,13 @@
         <v>1276</v>
       </c>
       <c r="H73" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I73" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J73" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="K73">
         <v>71</v>
@@ -7806,7 +7845,7 @@
         <v>21.82758621</v>
       </c>
       <c r="V73" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W73">
         <v>0.019322</v>
@@ -7835,10 +7874,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C74" s="2">
         <v>43905.36975553241</v>
@@ -7856,13 +7895,13 @@
         <v>1305</v>
       </c>
       <c r="H74" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I74" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J74" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K74">
         <v>64</v>
@@ -7886,7 +7925,7 @@
         <v>18.89655172</v>
       </c>
       <c r="V74" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W74">
         <v>-0.10107</v>
@@ -7915,10 +7954,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C75" s="2">
         <v>43905.37023015046</v>
@@ -7936,13 +7975,13 @@
         <v>1363</v>
       </c>
       <c r="H75" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I75" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J75" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="K75">
         <v>60</v>
@@ -7966,7 +8005,7 @@
         <v>17.25862069</v>
       </c>
       <c r="V75" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W75">
         <v>-0.02824</v>
@@ -7995,10 +8034,10 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B76" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C76" s="2">
         <v>43905.37062890046</v>
@@ -8016,13 +8055,13 @@
         <v>1392</v>
       </c>
       <c r="H76" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I76" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J76" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K76">
         <v>67</v>
@@ -8046,7 +8085,7 @@
         <v>18.20689655</v>
       </c>
       <c r="V76" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W76">
         <v>0.032699</v>
@@ -8075,10 +8114,10 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C77" s="2">
         <v>43905.37102997685</v>
@@ -8096,13 +8135,13 @@
         <v>1421</v>
       </c>
       <c r="H77" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I77" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="J77" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="K77">
         <v>68</v>
@@ -8126,7 +8165,7 @@
         <v>11.65517241</v>
       </c>
       <c r="V77" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W77">
         <v>-0.225922</v>
@@ -8155,10 +8194,10 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C78" s="2">
         <v>43905.37142820602</v>
@@ -8176,13 +8215,13 @@
         <v>1450</v>
       </c>
       <c r="H78" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I78" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="J78" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="K78">
         <v>63</v>
@@ -8206,7 +8245,7 @@
         <v>11.10344828</v>
       </c>
       <c r="V78" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W78">
         <v>-0.019025</v>
@@ -8235,10 +8274,10 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B79" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C79" s="2">
         <v>43905.37189575232</v>
@@ -8256,13 +8295,13 @@
         <v>1508</v>
       </c>
       <c r="H79" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I79" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J79" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="K79">
         <v>65</v>
@@ -8286,7 +8325,7 @@
         <v>13.29310345</v>
       </c>
       <c r="V79" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W79">
         <v>0.037753</v>
@@ -8315,10 +8354,10 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C80" s="2">
         <v>43905.37229842593</v>
@@ -8336,13 +8375,13 @@
         <v>1537</v>
       </c>
       <c r="H80" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I80" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J80" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="K80">
         <v>72</v>
@@ -8366,7 +8405,7 @@
         <v>14.37931034</v>
       </c>
       <c r="V80" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W80">
         <v>0.037455</v>
@@ -8395,10 +8434,10 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C81" s="2">
         <v>43905.37270165509</v>
@@ -8416,13 +8455,13 @@
         <v>1566</v>
       </c>
       <c r="H81" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I81" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J81" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="K81">
         <v>66</v>
@@ -8446,7 +8485,7 @@
         <v>22.51724138</v>
       </c>
       <c r="V81" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W81">
         <v>0.280618</v>
@@ -8475,10 +8514,10 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C82" s="2">
         <v>43905.37310010417</v>
@@ -8496,13 +8535,13 @@
         <v>1595</v>
       </c>
       <c r="H82" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I82" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J82" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="K82">
         <v>66</v>
@@ -8526,7 +8565,7 @@
         <v>18.20689655</v>
       </c>
       <c r="V82" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W82">
         <v>-0.148633</v>
@@ -8555,10 +8594,10 @@
     </row>
     <row r="83" spans="1:30">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C83" s="2">
         <v>43905.37357592593</v>
@@ -8576,13 +8615,13 @@
         <v>1653</v>
       </c>
       <c r="H83" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I83" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J83" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K83">
         <v>56</v>
@@ -8606,7 +8645,7 @@
         <v>18.62068966</v>
       </c>
       <c r="V83" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W83">
         <v>0.007134</v>
@@ -8635,10 +8674,10 @@
     </row>
     <row r="84" spans="1:30">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B84" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C84" s="2">
         <v>43905.37397979166</v>
@@ -8656,13 +8695,13 @@
         <v>1682</v>
       </c>
       <c r="H84" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I84" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J84" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="K84">
         <v>72</v>
@@ -8686,7 +8725,7 @@
         <v>18.75862069</v>
       </c>
       <c r="V84" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W84">
         <v>0.004756</v>
@@ -8715,10 +8754,10 @@
     </row>
     <row r="85" spans="1:30">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C85" s="2">
         <v>43905.37437518519</v>
@@ -8736,13 +8775,13 @@
         <v>1711</v>
       </c>
       <c r="H85" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I85" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J85" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K85">
         <v>73</v>
@@ -8766,7 +8805,7 @@
         <v>15.96551724</v>
       </c>
       <c r="V85" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W85">
         <v>-0.096314</v>
@@ -8795,10 +8834,10 @@
     </row>
     <row r="86" spans="1:30">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C86" s="2">
         <v>43905.37477902778</v>
@@ -8816,13 +8855,13 @@
         <v>1740</v>
       </c>
       <c r="H86" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I86" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J86" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="K86">
         <v>64</v>
@@ -8846,7 +8885,7 @@
         <v>19.5862069</v>
       </c>
       <c r="V86" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W86">
         <v>0.124851</v>
@@ -8875,10 +8914,10 @@
     </row>
     <row r="87" spans="1:30">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C87" s="2">
         <v>43905.3753066088</v>
@@ -8896,13 +8935,13 @@
         <v>1802</v>
       </c>
       <c r="H87" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I87" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J87" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="K87">
         <v>71</v>
@@ -8926,7 +8965,7 @@
         <v>12.06451613</v>
       </c>
       <c r="V87" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W87">
         <v>-0.121318</v>
@@ -8955,10 +8994,10 @@
     </row>
     <row r="88" spans="1:30">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B88" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C88" s="2">
         <v>43905.37570754629</v>
@@ -8976,13 +9015,13 @@
         <v>1831</v>
       </c>
       <c r="H88" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I88" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J88" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K88">
         <v>66</v>
@@ -9006,7 +9045,7 @@
         <v>14.34482759</v>
       </c>
       <c r="V88" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W88">
         <v>0.07863100000000001</v>
@@ -9035,10 +9074,10 @@
     </row>
     <row r="89" spans="1:30">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C89" s="2">
         <v>43905.37611783565</v>
@@ -9056,13 +9095,13 @@
         <v>1860</v>
       </c>
       <c r="H89" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I89" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J89" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K89">
         <v>70</v>
@@ -9086,7 +9125,7 @@
         <v>14.82758621</v>
       </c>
       <c r="V89" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W89">
         <v>0.016647</v>
@@ -9115,10 +9154,10 @@
     </row>
     <row r="90" spans="1:30">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B90" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C90" s="2">
         <v>43905.37651451389</v>
@@ -9136,13 +9175,13 @@
         <v>1889</v>
       </c>
       <c r="H90" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I90" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J90" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="K90">
         <v>73</v>
@@ -9166,7 +9205,7 @@
         <v>16.65517241</v>
       </c>
       <c r="V90" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W90">
         <v>0.06302000000000001</v>
@@ -9195,10 +9234,10 @@
     </row>
     <row r="91" spans="1:30">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B91" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C91" s="2">
         <v>43905.376594375</v>
@@ -9216,13 +9255,13 @@
         <v>1918</v>
       </c>
       <c r="H91" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I91" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J91" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="K91">
         <v>56</v>
@@ -9246,7 +9285,7 @@
         <v>16.17241379</v>
       </c>
       <c r="V91" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W91">
         <v>-0.016647</v>
@@ -9275,10 +9314,10 @@
     </row>
     <row r="92" spans="1:30">
       <c r="A92" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B92" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C92" s="2">
         <v>43905.37700059028</v>
@@ -9296,13 +9335,13 @@
         <v>1947</v>
       </c>
       <c r="H92" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I92" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J92" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="K92">
         <v>77</v>
@@ -9326,7 +9365,7 @@
         <v>18</v>
       </c>
       <c r="V92" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W92">
         <v>0.06302000000000001</v>
@@ -9355,10 +9394,10 @@
     </row>
     <row r="93" spans="1:30">
       <c r="A93" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C93" s="2">
         <v>43905.37740570602</v>
@@ -9376,13 +9415,13 @@
         <v>1976</v>
       </c>
       <c r="H93" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I93" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J93" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K93">
         <v>63</v>
@@ -9406,7 +9445,7 @@
         <v>15.27586207</v>
       </c>
       <c r="V93" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W93">
         <v>-0.09393600000000001</v>
@@ -9435,10 +9474,10 @@
     </row>
     <row r="94" spans="1:30">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B94" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C94" s="2">
         <v>43905.37781907408</v>
@@ -9456,13 +9495,13 @@
         <v>2005</v>
       </c>
       <c r="H94" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I94" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="J94" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="K94">
         <v>58</v>
@@ -9486,7 +9525,7 @@
         <v>13.44827586</v>
       </c>
       <c r="V94" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W94">
         <v>-0.06302000000000001</v>
@@ -9515,10 +9554,10 @@
     </row>
     <row r="95" spans="1:30">
       <c r="A95" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B95" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C95" s="2">
         <v>43905.37828546296</v>
@@ -9536,13 +9575,13 @@
         <v>2063</v>
       </c>
       <c r="H95" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I95" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J95" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K95">
         <v>62</v>
@@ -9566,7 +9605,7 @@
         <v>11.87931034</v>
       </c>
       <c r="V95" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W95">
         <v>-0.027051</v>
@@ -9595,10 +9634,10 @@
     </row>
     <row r="96" spans="1:30">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B96" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C96" s="2">
         <v>43905.37868584491</v>
@@ -9616,13 +9655,13 @@
         <v>2092</v>
       </c>
       <c r="H96" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I96" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J96" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K96">
         <v>70</v>
@@ -9646,7 +9685,7 @@
         <v>14.03448276</v>
       </c>
       <c r="V96" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W96">
         <v>0.07431599999999999</v>
@@ -9675,10 +9714,10 @@
     </row>
     <row r="97" spans="1:30">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B97" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C97" s="2">
         <v>43905.3790844213</v>
@@ -9696,13 +9735,13 @@
         <v>2121</v>
       </c>
       <c r="H97" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I97" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J97" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="K97">
         <v>73</v>
@@ -9726,7 +9765,7 @@
         <v>15.62068966</v>
       </c>
       <c r="V97" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W97">
         <v>0.054697</v>
@@ -9755,10 +9794,10 @@
     </row>
     <row r="98" spans="1:30">
       <c r="A98" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C98" s="2">
         <v>43905.37949032407</v>
@@ -9776,13 +9815,13 @@
         <v>2150</v>
       </c>
       <c r="H98" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I98" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J98" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="K98">
         <v>59</v>
@@ -9806,7 +9845,7 @@
         <v>17.65517241</v>
       </c>
       <c r="V98" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W98">
         <v>0.070155</v>
@@ -9835,10 +9874,10 @@
     </row>
     <row r="99" spans="1:30">
       <c r="A99" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B99" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C99" s="2">
         <v>43905.3799602662</v>
@@ -9856,13 +9895,13 @@
         <v>2208</v>
       </c>
       <c r="H99" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I99" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J99" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="K99">
         <v>60</v>
@@ -9886,7 +9925,7 @@
         <v>17.31034483</v>
       </c>
       <c r="V99" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W99">
         <v>-0.005945</v>
@@ -9915,10 +9954,10 @@
     </row>
     <row r="100" spans="1:30">
       <c r="A100" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C100" s="2">
         <v>43905.38074758102</v>
@@ -9936,13 +9975,13 @@
         <v>2266</v>
       </c>
       <c r="H100" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I100" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J100" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="K100">
         <v>77</v>
@@ -9966,7 +10005,7 @@
         <v>16.56896552</v>
       </c>
       <c r="V100" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W100">
         <v>-0.012782</v>
@@ -9995,10 +10034,10 @@
     </row>
     <row r="101" spans="1:30">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B101" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C101" s="2">
         <v>43905.38114480324</v>
@@ -10016,13 +10055,13 @@
         <v>2295</v>
       </c>
       <c r="H101" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I101" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J101" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="K101">
         <v>81</v>
@@ -10046,7 +10085,7 @@
         <v>13.24137931</v>
       </c>
       <c r="V101" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W101">
         <v>-0.114744</v>
@@ -10075,10 +10114,10 @@
     </row>
     <row r="102" spans="1:30">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B102" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C102" s="2">
         <v>43905.38153673611</v>
@@ -10096,13 +10135,13 @@
         <v>2324</v>
       </c>
       <c r="H102" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I102" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="J102" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="K102">
         <v>79</v>
@@ -10126,7 +10165,7 @@
         <v>10.17241379</v>
       </c>
       <c r="V102" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W102">
         <v>-0.105826</v>
@@ -10155,10 +10194,10 @@
     </row>
     <row r="103" spans="1:30">
       <c r="A103" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C103" s="2">
         <v>43905.381996875</v>
@@ -10176,13 +10215,13 @@
         <v>2382</v>
       </c>
       <c r="H103" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I103" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="J103" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="K103">
         <v>74</v>
@@ -10206,7 +10245,7 @@
         <v>9.62068966</v>
       </c>
       <c r="V103" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W103">
         <v>-0.009512</v>
@@ -10235,10 +10274,10 @@
     </row>
     <row r="104" spans="1:30">
       <c r="A104" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C104" s="2">
         <v>43905.38239262732</v>
@@ -10256,13 +10295,13 @@
         <v>2411</v>
       </c>
       <c r="H104" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I104" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J104" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="K104">
         <v>74</v>
@@ -10286,7 +10325,7 @@
         <v>11.65517241</v>
       </c>
       <c r="V104" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W104">
         <v>0.070155</v>
@@ -10315,10 +10354,10 @@
     </row>
     <row r="105" spans="1:30">
       <c r="A105" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C105" s="2">
         <v>43905.3831684375</v>
@@ -10336,13 +10375,13 @@
         <v>2469</v>
       </c>
       <c r="H105" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I105" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J105" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="K105">
         <v>83</v>
@@ -10366,7 +10405,7 @@
         <v>15.79310345</v>
       </c>
       <c r="V105" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W105">
         <v>0.071344</v>
@@ -10395,10 +10434,10 @@
     </row>
     <row r="106" spans="1:30">
       <c r="A106" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B106" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C106" s="2">
         <v>43905.38355795139</v>
@@ -10416,13 +10455,13 @@
         <v>2498</v>
       </c>
       <c r="H106" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I106" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J106" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="K106">
         <v>65</v>
@@ -10446,7 +10485,7 @@
         <v>19.89655172</v>
       </c>
       <c r="V106" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W106">
         <v>0.141498</v>
@@ -10475,10 +10514,10 @@
     </row>
     <row r="107" spans="1:30">
       <c r="A107" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C107" s="2">
         <v>43905.38401408565</v>
@@ -10496,13 +10535,13 @@
         <v>2556</v>
       </c>
       <c r="H107" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I107" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J107" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K107">
         <v>60</v>
@@ -10526,7 +10565,7 @@
         <v>20.82758621</v>
       </c>
       <c r="V107" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W107">
         <v>0.016052</v>
@@ -10555,10 +10594,10 @@
     </row>
     <row r="108" spans="1:30">
       <c r="A108" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C108" s="2">
         <v>43905.38478722222</v>
@@ -10576,13 +10615,13 @@
         <v>2614</v>
       </c>
       <c r="H108" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I108" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J108" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K108">
         <v>65</v>
@@ -10606,7 +10645,7 @@
         <v>22.96551724</v>
       </c>
       <c r="V108" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W108">
         <v>0.036861</v>
@@ -10635,10 +10674,10 @@
     </row>
     <row r="109" spans="1:30">
       <c r="A109" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B109" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C109" s="2">
         <v>43905.38518045139</v>
@@ -10656,13 +10695,13 @@
         <v>2643</v>
       </c>
       <c r="H109" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I109" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="J109" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="K109">
         <v>78</v>
@@ -10686,7 +10725,7 @@
         <v>23.06896552</v>
       </c>
       <c r="V109" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W109">
         <v>0.003567</v>
@@ -10715,10 +10754,10 @@
     </row>
     <row r="110" spans="1:30">
       <c r="A110" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C110" s="2">
         <v>43905.38557278935</v>
@@ -10736,13 +10775,13 @@
         <v>2672</v>
       </c>
       <c r="H110" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I110" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J110" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="K110">
         <v>102</v>
@@ -10766,7 +10805,7 @@
         <v>24.10344828</v>
       </c>
       <c r="V110" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W110">
         <v>0.035672</v>
@@ -10795,10 +10834,10 @@
     </row>
     <row r="111" spans="1:30">
       <c r="A111" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B111" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C111" s="2">
         <v>43905.38603423611</v>
@@ -10816,13 +10855,13 @@
         <v>2730</v>
       </c>
       <c r="H111" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I111" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J111" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="K111">
         <v>84</v>
@@ -10846,7 +10885,7 @@
         <v>15.27586207</v>
       </c>
       <c r="V111" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W111">
         <v>-0.1522</v>
@@ -10875,10 +10914,10 @@
     </row>
     <row r="112" spans="1:30">
       <c r="A112" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C112" s="2">
         <v>43905.38641778935</v>
@@ -10896,13 +10935,13 @@
         <v>2759</v>
       </c>
       <c r="H112" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I112" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="J112" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K112">
         <v>74</v>
@@ -10926,7 +10965,7 @@
         <v>16.4137931</v>
       </c>
       <c r="V112" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W112">
         <v>0.039239</v>
@@ -10955,10 +10994,10 @@
     </row>
     <row r="113" spans="1:30">
       <c r="A113" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B113" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C113" s="2">
         <v>43905.38679976852</v>
@@ -10976,13 +11015,13 @@
         <v>2788</v>
       </c>
       <c r="H113" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I113" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J113" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K113">
         <v>89</v>
@@ -11006,7 +11045,7 @@
         <v>19</v>
       </c>
       <c r="V113" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W113">
         <v>0.08918</v>
@@ -11035,10 +11074,10 @@
     </row>
     <row r="114" spans="1:30">
       <c r="A114" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B114" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C114" s="2">
         <v>43905.38757756945</v>
@@ -11056,13 +11095,13 @@
         <v>2846</v>
       </c>
       <c r="H114" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I114" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J114" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="K114">
         <v>62</v>
@@ -11086,7 +11125,7 @@
         <v>14.53448276</v>
       </c>
       <c r="V114" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W114">
         <v>-0.076992</v>
@@ -11115,10 +11154,10 @@
     </row>
     <row r="115" spans="1:30">
       <c r="A115" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C115" s="2">
         <v>43905.38801688657</v>
@@ -11136,13 +11175,13 @@
         <v>2904</v>
       </c>
       <c r="H115" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I115" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="J115" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K115">
         <v>60</v>
@@ -11166,7 +11205,7 @@
         <v>18.32758621</v>
       </c>
       <c r="V115" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W115">
         <v>0.065398</v>
@@ -11195,10 +11234,10 @@
     </row>
     <row r="116" spans="1:30">
       <c r="A116" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B116" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C116" s="2">
         <v>43905.38840190972</v>
@@ -11216,13 +11255,13 @@
         <v>2933</v>
       </c>
       <c r="H116" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I116" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="J116" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="K116">
         <v>60</v>
@@ -11246,7 +11285,7 @@
         <v>20.48275862</v>
       </c>
       <c r="V116" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W116">
         <v>0.07431599999999999</v>
@@ -11275,10 +11314,10 @@
     </row>
     <row r="117" spans="1:30">
       <c r="A117" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C117" s="2">
         <v>43905.38879309028</v>
@@ -11296,13 +11335,13 @@
         <v>2962</v>
       </c>
       <c r="H117" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I117" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J117" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="K117">
         <v>65</v>
@@ -11326,7 +11365,7 @@
         <v>25.79310345</v>
       </c>
       <c r="V117" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W117">
         <v>0.183115</v>
@@ -11355,10 +11394,10 @@
     </row>
     <row r="118" spans="1:30">
       <c r="A118" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C118" s="2">
         <v>43905.38918696759</v>
@@ -11376,13 +11415,13 @@
         <v>2991</v>
       </c>
       <c r="H118" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I118" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J118" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="K118">
         <v>75</v>
@@ -11406,7 +11445,7 @@
         <v>20.82758621</v>
       </c>
       <c r="V118" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W118">
         <v>-0.171225</v>
@@ -11435,10 +11474,10 @@
     </row>
     <row r="119" spans="1:30">
       <c r="A119" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B119" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C119" s="2">
         <v>43905.38957825232</v>
@@ -11456,13 +11495,13 @@
         <v>3020</v>
       </c>
       <c r="H119" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I119" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J119" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K119">
         <v>83</v>
@@ -11486,7 +11525,7 @@
         <v>18</v>
       </c>
       <c r="V119" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W119">
         <v>-0.09750300000000001</v>
@@ -11515,10 +11554,10 @@
     </row>
     <row r="120" spans="1:30">
       <c r="A120" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B120" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C120" s="2">
         <v>43905.39002297453</v>
@@ -11536,13 +11575,13 @@
         <v>3078</v>
       </c>
       <c r="H120" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I120" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J120" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="K120">
         <v>79</v>
@@ -11566,7 +11605,7 @@
         <v>12.27586207</v>
       </c>
       <c r="V120" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W120">
         <v>-0.098692</v>
@@ -11595,10 +11634,10 @@
     </row>
     <row r="121" spans="1:30">
       <c r="A121" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B121" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C121" s="2">
         <v>43905.3904039699</v>
@@ -11616,13 +11655,13 @@
         <v>3107</v>
       </c>
       <c r="H121" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I121" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J121" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="K121">
         <v>72</v>
@@ -11646,7 +11685,7 @@
         <v>8.48275862</v>
       </c>
       <c r="V121" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W121">
         <v>-0.130797</v>
@@ -11675,10 +11714,10 @@
     </row>
     <row r="122" spans="1:30">
       <c r="A122" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B122" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C122" s="2">
         <v>43905.3907987963</v>
@@ -11696,13 +11735,13 @@
         <v>3136</v>
       </c>
       <c r="H122" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I122" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J122" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="K122">
         <v>79</v>
@@ -11726,7 +11765,7 @@
         <v>12.44827586</v>
       </c>
       <c r="V122" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W122">
         <v>0.136742</v>
@@ -11755,10 +11794,10 @@
     </row>
     <row r="123" spans="1:30">
       <c r="A123" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B123" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C123" s="2">
         <v>43905.39118726852</v>
@@ -11776,13 +11815,13 @@
         <v>3165</v>
       </c>
       <c r="H123" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I123" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J123" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="K123">
         <v>84</v>
@@ -11806,7 +11845,7 @@
         <v>16.62068966</v>
       </c>
       <c r="V123" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W123">
         <v>0.143876</v>
@@ -11835,10 +11874,10 @@
     </row>
     <row r="124" spans="1:30">
       <c r="A124" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B124" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C124" s="2">
         <v>43905.39156853009</v>
@@ -11856,13 +11895,13 @@
         <v>3194</v>
       </c>
       <c r="H124" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I124" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J124" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="K124">
         <v>75</v>
@@ -11886,7 +11925,7 @@
         <v>17.10344828</v>
       </c>
       <c r="V124" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W124">
         <v>0.016647</v>
@@ -11915,10 +11954,10 @@
     </row>
     <row r="125" spans="1:30">
       <c r="A125" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B125" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C125" s="2">
         <v>43905.39196420139</v>
@@ -11936,13 +11975,13 @@
         <v>3223</v>
       </c>
       <c r="H125" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I125" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J125" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="K125">
         <v>76</v>
@@ -11966,7 +12005,7 @@
         <v>21.37931034</v>
       </c>
       <c r="V125" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W125">
         <v>0.147444</v>
@@ -11995,10 +12034,10 @@
     </row>
     <row r="126" spans="1:30">
       <c r="A126" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B126" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C126" s="2">
         <v>43905.39203550926</v>
@@ -12016,13 +12055,13 @@
         <v>3252</v>
       </c>
       <c r="H126" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I126" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="J126" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="K126">
         <v>78</v>
@@ -12046,7 +12085,7 @@
         <v>22.17241379</v>
       </c>
       <c r="V126" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W126">
         <v>0.027348</v>
@@ -12075,10 +12114,10 @@
     </row>
     <row r="127" spans="1:30">
       <c r="A127" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B127" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C127" s="2">
         <v>43905.39242384259</v>
@@ -12096,13 +12135,13 @@
         <v>3281</v>
       </c>
       <c r="H127" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I127" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J127" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="K127">
         <v>94</v>
@@ -12126,7 +12165,7 @@
         <v>20.37931034</v>
       </c>
       <c r="V127" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W127">
         <v>-0.061831</v>
@@ -12155,10 +12194,10 @@
     </row>
     <row r="128" spans="1:30">
       <c r="A128" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B128" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C128" s="2">
         <v>43905.39359981482</v>
@@ -12176,13 +12215,13 @@
         <v>3368</v>
       </c>
       <c r="H128" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I128" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J128" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="K128">
         <v>90</v>
@@ -12206,7 +12245,7 @@
         <v>17.08045977</v>
       </c>
       <c r="V128" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W128">
         <v>-0.037918</v>
@@ -12235,10 +12274,10 @@
     </row>
     <row r="129" spans="1:30">
       <c r="A129" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B129" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C129" s="2">
         <v>43905.39406228009</v>
@@ -12256,13 +12295,13 @@
         <v>3426</v>
       </c>
       <c r="H129" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I129" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="J129" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="K129">
         <v>85</v>
@@ -12286,7 +12325,7 @@
         <v>12.56896552</v>
       </c>
       <c r="V129" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W129">
         <v>-0.07778400000000001</v>
@@ -12315,10 +12354,10 @@
     </row>
     <row r="130" spans="1:30">
       <c r="A130" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B130" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C130" s="2">
         <v>43905.39445508102</v>
@@ -12336,13 +12375,13 @@
         <v>3455</v>
       </c>
       <c r="H130" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I130" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J130" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="K130">
         <v>81</v>
@@ -12366,7 +12405,7 @@
         <v>24.06896552</v>
       </c>
       <c r="V130" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W130">
         <v>0.396552</v>
@@ -12395,10 +12434,10 @@
     </row>
     <row r="131" spans="1:30">
       <c r="A131" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B131" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C131" s="2">
         <v>43905.39484420139</v>
@@ -12416,13 +12455,13 @@
         <v>3484</v>
       </c>
       <c r="H131" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I131" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J131" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="K131">
         <v>88</v>
@@ -12446,7 +12485,7 @@
         <v>24.44827586</v>
       </c>
       <c r="V131" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W131">
         <v>0.01308</v>
@@ -12475,10 +12514,10 @@
     </row>
     <row r="132" spans="1:30">
       <c r="A132" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B132" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C132" s="2">
         <v>43905.39523104166</v>
@@ -12496,13 +12535,13 @@
         <v>3513</v>
       </c>
       <c r="H132" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I132" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="J132" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="K132">
         <v>92</v>
@@ -12526,7 +12565,7 @@
         <v>23.89655172</v>
       </c>
       <c r="V132" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W132">
         <v>-0.019025</v>
@@ -12555,10 +12594,10 @@
     </row>
     <row r="133" spans="1:30">
       <c r="A133" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B133" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C133" s="2">
         <v>43905.39608542824</v>
@@ -12576,13 +12615,13 @@
         <v>3600</v>
       </c>
       <c r="H133" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I133" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="J133" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="K133">
         <v>103</v>
@@ -12606,7 +12645,7 @@
         <v>26.24137931</v>
       </c>
       <c r="V133" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W133">
         <v>0.026952</v>
@@ -12635,10 +12674,10 @@
     </row>
     <row r="134" spans="1:30">
       <c r="A134" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B134" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C134" s="2">
         <v>43905.39647616898</v>
@@ -12656,13 +12695,13 @@
         <v>3629</v>
       </c>
       <c r="H134" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I134" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J134" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="K134">
         <v>104</v>
@@ -12686,7 +12725,7 @@
         <v>18.89655172</v>
       </c>
       <c r="V134" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W134">
         <v>-0.25327</v>
@@ -12715,10 +12754,10 @@
     </row>
     <row r="135" spans="1:30">
       <c r="A135" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B135" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C135" s="2">
         <v>43905.39686945602</v>
@@ -12736,13 +12775,13 @@
         <v>3658</v>
       </c>
       <c r="H135" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I135" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="J135" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="K135">
         <v>85</v>
@@ -12766,7 +12805,7 @@
         <v>11.44827586</v>
       </c>
       <c r="V135" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W135">
         <v>-0.256837</v>
@@ -12795,10 +12834,10 @@
     </row>
     <row r="136" spans="1:30">
       <c r="A136" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B136" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C136" s="2">
         <v>43905.39726204861</v>
@@ -12816,13 +12855,13 @@
         <v>3687</v>
       </c>
       <c r="H136" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I136" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="J136" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="K136">
         <v>85</v>
@@ -12846,7 +12885,7 @@
         <v>8.68965517</v>
       </c>
       <c r="V136" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W136">
         <v>-0.095125</v>
@@ -12875,10 +12914,10 @@
     </row>
     <row r="137" spans="1:30">
       <c r="A137" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B137" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C137" s="2">
         <v>43905.39810152777</v>
@@ -12896,13 +12935,13 @@
         <v>3774</v>
       </c>
       <c r="H137" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I137" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="J137" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="K137">
         <v>98</v>
@@ -12926,7 +12965,7 @@
         <v>13.91954023</v>
       </c>
       <c r="V137" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W137">
         <v>0.060114</v>
@@ -12955,10 +12994,10 @@
     </row>
     <row r="138" spans="1:30">
       <c r="A138" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B138" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C138" s="2">
         <v>43905.39889516203</v>
@@ -12976,13 +13015,13 @@
         <v>3832</v>
       </c>
       <c r="H138" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I138" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="J138" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="K138">
         <v>106</v>
@@ -13006,7 +13045,7 @@
         <v>20.31034483</v>
       </c>
       <c r="V138" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W138">
         <v>0.110186</v>
@@ -13035,10 +13074,10 @@
     </row>
     <row r="139" spans="1:30">
       <c r="A139" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B139" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C139" s="2">
         <v>43905.39929194444</v>
@@ -13056,13 +13095,13 @@
         <v>3861</v>
       </c>
       <c r="H139" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I139" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="J139" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="K139">
         <v>110</v>
@@ -13086,7 +13125,7 @@
         <v>18.34482759</v>
       </c>
       <c r="V139" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W139">
         <v>-0.067776</v>
@@ -13115,10 +13154,10 @@
     </row>
     <row r="140" spans="1:30">
       <c r="A140" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B140" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C140" s="2">
         <v>43905.39976372685</v>
@@ -13136,13 +13175,13 @@
         <v>3919</v>
       </c>
       <c r="H140" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I140" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="J140" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="K140">
         <v>99</v>
@@ -13166,7 +13205,7 @@
         <v>16.84482759</v>
       </c>
       <c r="V140" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W140">
         <v>-0.025862</v>
@@ -13195,10 +13234,10 @@
     </row>
     <row r="141" spans="1:30">
       <c r="A141" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B141" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C141" s="2">
         <v>43905.40017170139</v>
@@ -13216,13 +13255,13 @@
         <v>3948</v>
       </c>
       <c r="H141" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I141" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="J141" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="K141">
         <v>92</v>
@@ -13246,7 +13285,7 @@
         <v>8.275862070000001</v>
       </c>
       <c r="V141" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W141">
         <v>-0.295482</v>
@@ -13275,10 +13314,10 @@
     </row>
     <row r="142" spans="1:30">
       <c r="A142" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B142" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C142" s="2">
         <v>43905.40057579861</v>
@@ -13296,13 +13335,13 @@
         <v>3977</v>
       </c>
       <c r="H142" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I142" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="J142" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="K142">
         <v>88</v>
@@ -13326,7 +13365,7 @@
         <v>5.55172414</v>
       </c>
       <c r="V142" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W142">
         <v>-0.09393600000000001</v>
@@ -13355,10 +13394,10 @@
     </row>
     <row r="143" spans="1:30">
       <c r="A143" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B143" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C143" s="2">
         <v>43905.40097962963</v>
@@ -13376,13 +13415,13 @@
         <v>4006</v>
       </c>
       <c r="H143" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I143" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="J143" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="K143">
         <v>103</v>
@@ -13406,7 +13445,7 @@
         <v>10.72413793</v>
       </c>
       <c r="V143" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W143">
         <v>0.178359</v>
@@ -13435,10 +13474,10 @@
     </row>
     <row r="144" spans="1:30">
       <c r="A144" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B144" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C144" s="2">
         <v>43905.40145209491</v>
@@ -13456,13 +13495,13 @@
         <v>4064</v>
       </c>
       <c r="H144" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I144" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="J144" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K144">
         <v>103</v>
@@ -13486,7 +13525,7 @@
         <v>16.81034483</v>
       </c>
       <c r="V144" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W144">
         <v>0.104935</v>
@@ -13515,10 +13554,10 @@
     </row>
     <row r="145" spans="1:30">
       <c r="A145" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B145" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C145" s="2">
         <v>43905.40186480324</v>
@@ -13536,13 +13575,13 @@
         <v>4093</v>
       </c>
       <c r="H145" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I145" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="J145" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="K145">
         <v>97</v>
@@ -13566,7 +13605,7 @@
         <v>15.62068966</v>
       </c>
       <c r="V145" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W145">
         <v>-0.041023</v>
@@ -13595,10 +13634,10 @@
     </row>
     <row r="146" spans="1:30">
       <c r="A146" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B146" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C146" s="2">
         <v>43905.40227127315</v>
@@ -13616,13 +13655,13 @@
         <v>4122</v>
       </c>
       <c r="H146" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I146" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="J146" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="K146">
         <v>96</v>
@@ -13646,7 +13685,7 @@
         <v>16.72413793</v>
       </c>
       <c r="V146" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W146">
         <v>0.03805</v>
@@ -13675,10 +13714,10 @@
     </row>
     <row r="147" spans="1:30">
       <c r="A147" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B147" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C147" s="2">
         <v>43905.40267277777</v>
@@ -13696,13 +13735,13 @@
         <v>4151</v>
       </c>
       <c r="H147" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I147" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="J147" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="K147">
         <v>95</v>
@@ -13726,7 +13765,7 @@
         <v>17.31034483</v>
       </c>
       <c r="V147" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W147">
         <v>0.020214</v>
@@ -13755,10 +13794,10 @@
     </row>
     <row r="148" spans="1:30">
       <c r="A148" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B148" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C148" s="2">
         <v>43905.40316255787</v>
@@ -13776,13 +13815,13 @@
         <v>4209</v>
       </c>
       <c r="H148" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I148" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J148" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="K148">
         <v>92</v>
@@ -13806,7 +13845,7 @@
         <v>17.94827586</v>
       </c>
       <c r="V148" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W148">
         <v>0.010999</v>
@@ -13835,10 +13874,10 @@
     </row>
     <row r="149" spans="1:30">
       <c r="A149" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B149" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C149" s="2">
         <v>43905.40357260417</v>
@@ -13856,13 +13895,13 @@
         <v>4238</v>
       </c>
       <c r="H149" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I149" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="J149" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="K149">
         <v>95</v>
@@ -13886,7 +13925,7 @@
         <v>15.37931034</v>
       </c>
       <c r="V149" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W149">
         <v>-0.088585</v>
@@ -13915,10 +13954,10 @@
     </row>
     <row r="150" spans="1:30">
       <c r="A150" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B150" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C150" s="2">
         <v>43905.40397891204</v>
@@ -13936,13 +13975,13 @@
         <v>4267</v>
       </c>
       <c r="H150" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I150" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="J150" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="K150">
         <v>90</v>
@@ -13966,7 +14005,7 @@
         <v>15.27586207</v>
       </c>
       <c r="V150" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W150">
         <v>-0.003567</v>
@@ -13995,10 +14034,10 @@
     </row>
     <row r="151" spans="1:30">
       <c r="A151" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B151" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C151" s="2">
         <v>43905.40446133102</v>
@@ -14016,13 +14055,13 @@
         <v>4325</v>
       </c>
       <c r="H151" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I151" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="J151" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="K151">
         <v>89</v>
@@ -14046,7 +14085,7 @@
         <v>12.15517241</v>
       </c>
       <c r="V151" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W151">
         <v>-0.053805</v>
@@ -14075,10 +14114,10 @@
     </row>
     <row r="152" spans="1:30">
       <c r="A152" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B152" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C152" s="2">
         <v>43905.40485790509</v>
@@ -14096,13 +14135,13 @@
         <v>4354</v>
       </c>
       <c r="H152" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I152" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="J152" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="K152">
         <v>87</v>
@@ -14126,7 +14165,7 @@
         <v>11.79310345</v>
       </c>
       <c r="V152" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W152">
         <v>-0.012485</v>
@@ -14155,10 +14194,10 @@
     </row>
     <row r="153" spans="1:30">
       <c r="A153" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B153" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C153" s="2">
         <v>43905.40527519676</v>
@@ -14176,13 +14215,13 @@
         <v>4383</v>
       </c>
       <c r="H153" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I153" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="J153" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K153">
         <v>79</v>
@@ -14206,7 +14245,7 @@
         <v>17.86206897</v>
       </c>
       <c r="V153" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W153">
         <v>0.209275</v>
@@ -14235,10 +14274,10 @@
     </row>
     <row r="154" spans="1:30">
       <c r="A154" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B154" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C154" s="2">
         <v>43905.40568210648</v>
@@ -14256,13 +14295,13 @@
         <v>4412</v>
       </c>
       <c r="H154" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I154" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="J154" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="K154">
         <v>76</v>
@@ -14286,7 +14325,7 @@
         <v>19.79310345</v>
       </c>
       <c r="V154" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W154">
         <v>0.06658699999999999</v>
@@ -14315,10 +14354,10 @@
     </row>
     <row r="155" spans="1:30">
       <c r="A155" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B155" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C155" s="2">
         <v>43905.40616476852</v>
@@ -14336,13 +14375,13 @@
         <v>4470</v>
       </c>
       <c r="H155" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I155" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="J155" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K155">
         <v>88</v>
@@ -14366,7 +14405,7 @@
         <v>21.72413793</v>
       </c>
       <c r="V155" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="W155">
         <v>0.033294</v>
@@ -14405,102 +14444,102 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2">
         <v>43905.40656033565</v>
@@ -14518,13 +14557,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="J2" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K2">
         <v>78</v>
@@ -14548,7 +14587,7 @@
         <v>-22.17241379</v>
       </c>
       <c r="V2" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="X2">
         <v>-22.172414</v>
@@ -14559,10 +14598,10 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C3" s="2">
         <v>43905.40696612268</v>
@@ -14580,13 +14619,13 @@
         <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I3" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="J3" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="K3">
         <v>89</v>
@@ -14610,7 +14649,7 @@
         <v>-101.5862069</v>
       </c>
       <c r="V3" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W3">
         <v>-2.738407</v>
@@ -14633,10 +14672,10 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2">
         <v>43905.40736842593</v>
@@ -14654,13 +14693,13 @@
         <v>58</v>
       </c>
       <c r="H4" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I4" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="J4" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="K4">
         <v>119</v>
@@ -14684,7 +14723,7 @@
         <v>-90.41379310000001</v>
       </c>
       <c r="V4" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W4">
         <v>0.385256</v>
@@ -14713,10 +14752,10 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C5" s="2">
         <v>43905.40785921297</v>
@@ -14734,13 +14773,13 @@
         <v>116</v>
       </c>
       <c r="H5" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I5" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="J5" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="K5">
         <v>117</v>
@@ -14764,7 +14803,7 @@
         <v>-82.15517241000001</v>
       </c>
       <c r="V5" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W5">
         <v>0.14239</v>
@@ -14793,10 +14832,10 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2">
         <v>43905.40825150463</v>
@@ -14814,13 +14853,13 @@
         <v>145</v>
       </c>
       <c r="H6" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I6" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="J6" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K6">
         <v>108</v>
@@ -14844,7 +14883,7 @@
         <v>-73.75862069</v>
       </c>
       <c r="V6" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W6">
         <v>0.289536</v>
@@ -14873,10 +14912,10 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C7" s="2">
         <v>43905.40865800926</v>
@@ -14894,13 +14933,13 @@
         <v>174</v>
       </c>
       <c r="H7" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I7" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="J7" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="K7">
         <v>73</v>
@@ -14924,7 +14963,7 @@
         <v>-71.27586207</v>
       </c>
       <c r="V7" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W7">
         <v>0.08561199999999999</v>
@@ -14953,10 +14992,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2">
         <v>43905.40954530093</v>
@@ -14974,13 +15013,13 @@
         <v>261</v>
       </c>
       <c r="H8" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I8" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="J8" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="K8">
         <v>87</v>
@@ -15004,7 +15043,7 @@
         <v>-68.94252874</v>
       </c>
       <c r="V8" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W8">
         <v>0.02682</v>
@@ -15033,10 +15072,10 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2">
         <v>43905.40993851852</v>
@@ -15054,13 +15093,13 @@
         <v>290</v>
       </c>
       <c r="H9" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I9" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J9" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="K9">
         <v>84</v>
@@ -15084,7 +15123,7 @@
         <v>-56.79310345</v>
       </c>
       <c r="V9" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W9">
         <v>0.418946</v>
@@ -15113,10 +15152,10 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2">
         <v>43905.41034855324</v>
@@ -15134,13 +15173,13 @@
         <v>319</v>
       </c>
       <c r="H10" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I10" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="J10" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="K10">
         <v>93</v>
@@ -15164,7 +15203,7 @@
         <v>-53.51724138</v>
       </c>
       <c r="V10" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W10">
         <v>0.112961</v>
@@ -15193,10 +15232,10 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C11" s="2">
         <v>43905.41074886574</v>
@@ -15214,13 +15253,13 @@
         <v>348</v>
       </c>
       <c r="H11" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I11" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="J11" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="K11">
         <v>53</v>
@@ -15244,7 +15283,7 @@
         <v>-46.96551724</v>
       </c>
       <c r="V11" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W11">
         <v>0.225922</v>
@@ -15273,10 +15312,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C12" s="2">
         <v>43905.41122502315</v>
@@ -15294,13 +15333,13 @@
         <v>406</v>
       </c>
       <c r="H12" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I12" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="J12" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="K12">
         <v>60</v>
@@ -15324,7 +15363,7 @@
         <v>-45.87931034</v>
       </c>
       <c r="V12" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W12">
         <v>0.018728</v>
@@ -15353,10 +15392,10 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C13" s="2">
         <v>43905.41162112269</v>
@@ -15374,13 +15413,13 @@
         <v>435</v>
       </c>
       <c r="H13" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I13" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="J13" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="K13">
         <v>65</v>
@@ -15404,7 +15443,7 @@
         <v>-48.10344828</v>
       </c>
       <c r="V13" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W13">
         <v>-0.076694</v>
@@ -15433,10 +15472,10 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2">
         <v>43905.41203418982</v>
@@ -15454,13 +15493,13 @@
         <v>464</v>
       </c>
       <c r="H14" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I14" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="J14" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K14">
         <v>83</v>
@@ -15484,7 +15523,7 @@
         <v>-50.79310345</v>
       </c>
       <c r="V14" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W14">
         <v>-0.092747</v>
@@ -15513,10 +15552,10 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C15" s="2">
         <v>43905.41243891204</v>
@@ -15534,13 +15573,13 @@
         <v>493</v>
       </c>
       <c r="H15" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I15" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J15" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="K15">
         <v>92</v>
@@ -15564,7 +15603,7 @@
         <v>-49.79310345</v>
       </c>
       <c r="V15" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W15">
         <v>0.034483</v>
@@ -15593,10 +15632,10 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C16" s="2">
         <v>43905.4125115162</v>
@@ -15614,13 +15653,13 @@
         <v>522</v>
       </c>
       <c r="H16" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I16" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="J16" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="K16">
         <v>57</v>
@@ -15644,7 +15683,7 @@
         <v>-47.17241379</v>
       </c>
       <c r="V16" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W16">
         <v>0.090369</v>
@@ -15673,10 +15712,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C17" s="2">
         <v>43905.41291292824</v>
@@ -15694,13 +15733,13 @@
         <v>551</v>
       </c>
       <c r="H17" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I17" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="J17" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="K17">
         <v>80</v>
@@ -15724,7 +15763,7 @@
         <v>-42.55172414</v>
       </c>
       <c r="V17" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W17">
         <v>0.159334</v>
@@ -15753,10 +15792,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C18" s="2">
         <v>43905.41330755787</v>
@@ -15774,13 +15813,13 @@
         <v>580</v>
       </c>
       <c r="H18" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I18" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J18" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K18">
         <v>84</v>
@@ -15804,7 +15843,7 @@
         <v>-43.10344828</v>
       </c>
       <c r="V18" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W18">
         <v>-0.019025</v>
@@ -15833,10 +15872,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2">
         <v>43905.4137133912</v>
@@ -15854,13 +15893,13 @@
         <v>609</v>
       </c>
       <c r="H19" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I19" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="J19" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="K19">
         <v>74</v>
@@ -15884,7 +15923,7 @@
         <v>-37</v>
       </c>
       <c r="V19" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W19">
         <v>0.210464</v>
@@ -15913,10 +15952,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C20" s="2">
         <v>43905.41410821759</v>
@@ -15934,13 +15973,13 @@
         <v>638</v>
       </c>
       <c r="H20" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I20" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="J20" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K20">
         <v>89</v>
@@ -15964,7 +16003,7 @@
         <v>-35.86206897</v>
       </c>
       <c r="V20" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W20">
         <v>0.039239</v>
@@ -15993,10 +16032,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C21" s="2">
         <v>43905.41418798611</v>
@@ -16014,13 +16053,13 @@
         <v>667</v>
       </c>
       <c r="H21" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I21" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="J21" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="K21">
         <v>86</v>
@@ -16044,7 +16083,7 @@
         <v>-34.51724138</v>
       </c>
       <c r="V21" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W21">
         <v>0.046373</v>
@@ -16073,10 +16112,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C22" s="2">
         <v>43905.41459003472</v>
@@ -16094,13 +16133,13 @@
         <v>696</v>
       </c>
       <c r="H22" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I22" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="J22" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K22">
         <v>80</v>
@@ -16124,7 +16163,7 @@
         <v>-31.68965517</v>
       </c>
       <c r="V22" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W22">
         <v>0.09750300000000001</v>
@@ -16153,10 +16192,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C23" s="2">
         <v>43905.41498318287</v>
@@ -16174,13 +16213,13 @@
         <v>725</v>
       </c>
       <c r="H23" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I23" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="J23" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="K23">
         <v>71</v>
@@ -16204,7 +16243,7 @@
         <v>-29.51724138</v>
       </c>
       <c r="V23" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W23">
         <v>0.07491100000000001</v>
@@ -16233,10 +16272,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2">
         <v>43905.41538748843</v>
@@ -16254,13 +16293,13 @@
         <v>754</v>
       </c>
       <c r="H24" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I24" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="J24" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K24">
         <v>69</v>
@@ -16284,7 +16323,7 @@
         <v>-30.89655172</v>
       </c>
       <c r="V24" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W24">
         <v>-0.047562</v>
@@ -16313,10 +16352,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2">
         <v>43905.41578619213</v>
@@ -16334,13 +16373,13 @@
         <v>783</v>
       </c>
       <c r="H25" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I25" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="J25" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="K25">
         <v>76</v>
@@ -16364,7 +16403,7 @@
         <v>-32.79310345</v>
       </c>
       <c r="V25" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W25">
         <v>-0.065398</v>
@@ -16393,10 +16432,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C26" s="2">
         <v>43905.41586673611</v>
@@ -16414,13 +16453,13 @@
         <v>812</v>
       </c>
       <c r="H26" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I26" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J26" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="K26">
         <v>72</v>
@@ -16444,7 +16483,7 @@
         <v>-34.17241379</v>
       </c>
       <c r="V26" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W26">
         <v>-0.047562</v>
@@ -16473,10 +16512,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C27" s="2">
         <v>43905.41627064815</v>
@@ -16494,13 +16533,13 @@
         <v>841</v>
       </c>
       <c r="H27" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I27" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="J27" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="K27">
         <v>65</v>
@@ -16524,7 +16563,7 @@
         <v>-34.96551724</v>
       </c>
       <c r="V27" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W27">
         <v>-0.027348</v>
@@ -16553,10 +16592,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C28" s="2">
         <v>43905.41666415509</v>
@@ -16574,13 +16613,13 @@
         <v>870</v>
       </c>
       <c r="H28" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I28" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="J28" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="K28">
         <v>61</v>
@@ -16604,7 +16643,7 @@
         <v>-34.17241379</v>
       </c>
       <c r="V28" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W28">
         <v>0.027348</v>
@@ -16633,10 +16672,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C29" s="2">
         <v>43905.41711885417</v>
@@ -16654,13 +16693,13 @@
         <v>903</v>
       </c>
       <c r="H29" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I29" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="J29" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="K29">
         <v>53</v>
@@ -16684,7 +16723,7 @@
         <v>-33.81818182</v>
       </c>
       <c r="V29" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W29">
         <v>0.010734</v>
@@ -16713,10 +16752,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2">
         <v>43905.41760005787</v>
@@ -16734,13 +16773,13 @@
         <v>961</v>
       </c>
       <c r="H30" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I30" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="J30" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="K30">
         <v>65</v>
@@ -16764,7 +16803,7 @@
         <v>-27.94827586</v>
       </c>
       <c r="V30" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W30">
         <v>0.101205</v>
@@ -16793,10 +16832,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C31" s="2">
         <v>43905.41798528935</v>
@@ -16814,13 +16853,13 @@
         <v>990</v>
       </c>
       <c r="H31" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I31" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="J31" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="K31">
         <v>62</v>
@@ -16844,7 +16883,7 @@
         <v>-25.55172414</v>
       </c>
       <c r="V31" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W31">
         <v>0.08264000000000001</v>
@@ -16873,10 +16912,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2">
         <v>43905.41839347222</v>
@@ -16894,13 +16933,13 @@
         <v>1019</v>
       </c>
       <c r="H32" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I32" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="J32" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="K32">
         <v>65</v>
@@ -16924,7 +16963,7 @@
         <v>-25.79310345</v>
       </c>
       <c r="V32" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W32">
         <v>-0.008323000000000001</v>
@@ -16953,10 +16992,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C33" s="2">
         <v>43905.41879380787</v>
@@ -16974,13 +17013,13 @@
         <v>1048</v>
       </c>
       <c r="H33" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I33" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="J33" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K33">
         <v>64</v>
@@ -17004,7 +17043,7 @@
         <v>-25.93103448</v>
       </c>
       <c r="V33" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W33">
         <v>-0.004756</v>
@@ -17033,10 +17072,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C34" s="2">
         <v>43905.41919268519</v>
@@ -17054,13 +17093,13 @@
         <v>1077</v>
       </c>
       <c r="H34" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I34" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="J34" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="K34">
         <v>58</v>
@@ -17084,7 +17123,7 @@
         <v>-26.34482759</v>
       </c>
       <c r="V34" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W34">
         <v>-0.014269</v>
@@ -17113,10 +17152,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C35" s="2">
         <v>43905.41965954861</v>
@@ -17134,13 +17173,13 @@
         <v>1135</v>
       </c>
       <c r="H35" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I35" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="J35" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K35">
         <v>60</v>
@@ -17164,7 +17203,7 @@
         <v>-25.5862069</v>
       </c>
       <c r="V35" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W35">
         <v>0.01308</v>
@@ -17193,10 +17232,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C36" s="2">
         <v>43905.4200671875</v>
@@ -17214,13 +17253,13 @@
         <v>1164</v>
       </c>
       <c r="H36" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I36" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="J36" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="K36">
         <v>70</v>
@@ -17244,7 +17283,7 @@
         <v>-25.89655172</v>
       </c>
       <c r="V36" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W36">
         <v>-0.010702</v>
@@ -17273,10 +17312,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C37" s="2">
         <v>43905.42046076389</v>
@@ -17294,13 +17333,13 @@
         <v>1193</v>
       </c>
       <c r="H37" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I37" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="J37" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="K37">
         <v>57</v>
@@ -17324,7 +17363,7 @@
         <v>-25.79310345</v>
       </c>
       <c r="V37" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W37">
         <v>0.003567</v>
@@ -17353,10 +17392,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C38" s="2">
         <v>43905.42085435185</v>
@@ -17374,13 +17413,13 @@
         <v>1222</v>
       </c>
       <c r="H38" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I38" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="J38" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="K38">
         <v>63</v>
@@ -17404,7 +17443,7 @@
         <v>-25</v>
       </c>
       <c r="V38" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W38">
         <v>0.027348</v>
@@ -17433,10 +17472,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C39" s="2">
         <v>43905.42130972222</v>
@@ -17454,13 +17493,13 @@
         <v>1280</v>
       </c>
       <c r="H39" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I39" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="J39" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="K39">
         <v>71</v>
@@ -17484,7 +17523,7 @@
         <v>-24.89655172</v>
       </c>
       <c r="V39" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W39">
         <v>0.001784</v>
@@ -17513,10 +17552,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C40" s="2">
         <v>43905.42170667824</v>
@@ -17534,13 +17573,13 @@
         <v>1309</v>
       </c>
       <c r="H40" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I40" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="J40" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="K40">
         <v>57</v>
@@ -17564,7 +17603,7 @@
         <v>-23.86206897</v>
       </c>
       <c r="V40" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W40">
         <v>0.035672</v>
@@ -17593,10 +17632,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C41" s="2">
         <v>43905.42209358796</v>
@@ -17614,13 +17653,13 @@
         <v>1338</v>
       </c>
       <c r="H41" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I41" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J41" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="K41">
         <v>77</v>
@@ -17644,7 +17683,7 @@
         <v>-22.86206897</v>
       </c>
       <c r="V41" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W41">
         <v>0.034483</v>
@@ -17673,10 +17712,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C42" s="2">
         <v>43905.42249329861</v>
@@ -17694,13 +17733,13 @@
         <v>1367</v>
       </c>
       <c r="H42" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I42" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="J42" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="K42">
         <v>80</v>
@@ -17724,7 +17763,7 @@
         <v>-22.51724138</v>
       </c>
       <c r="V42" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W42">
         <v>0.011891</v>
@@ -17753,10 +17792,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C43" s="2">
         <v>43905.42288127315</v>
@@ -17774,13 +17813,13 @@
         <v>1396</v>
       </c>
       <c r="H43" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I43" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="J43" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="K43">
         <v>79</v>
@@ -17804,7 +17843,7 @@
         <v>-21.72413793</v>
       </c>
       <c r="V43" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W43">
         <v>0.027348</v>
@@ -17833,10 +17872,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C44" s="2">
         <v>43905.42333550926</v>
@@ -17854,13 +17893,13 @@
         <v>1454</v>
       </c>
       <c r="H44" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I44" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="J44" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="K44">
         <v>90</v>
@@ -17884,7 +17923,7 @@
         <v>-21.27586207</v>
       </c>
       <c r="V44" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W44">
         <v>0.007729</v>
@@ -17913,10 +17952,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C45" s="2">
         <v>43905.42372643518</v>
@@ -17934,13 +17973,13 @@
         <v>1483</v>
       </c>
       <c r="H45" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I45" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="J45" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="K45">
         <v>66</v>
@@ -17964,7 +18003,7 @@
         <v>-21.48275862</v>
       </c>
       <c r="V45" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W45">
         <v>-0.007134</v>
@@ -17993,10 +18032,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C46" s="2">
         <v>43905.42411983796</v>
@@ -18014,13 +18053,13 @@
         <v>1512</v>
       </c>
       <c r="H46" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I46" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="J46" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K46">
         <v>77</v>
@@ -18044,7 +18083,7 @@
         <v>-21.06896552</v>
       </c>
       <c r="V46" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W46">
         <v>0.014269</v>
@@ -18073,10 +18112,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C47" s="2">
         <v>43905.4245116551</v>
@@ -18094,13 +18133,13 @@
         <v>1541</v>
       </c>
       <c r="H47" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I47" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="J47" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="K47">
         <v>66</v>
@@ -18124,7 +18163,7 @@
         <v>-21.13793103</v>
       </c>
       <c r="V47" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W47">
         <v>-0.002378</v>
@@ -18153,10 +18192,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C48" s="2">
         <v>43905.4248938426</v>
@@ -18174,13 +18213,13 @@
         <v>1570</v>
       </c>
       <c r="H48" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I48" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="J48" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="K48">
         <v>81</v>
@@ -18204,7 +18243,7 @@
         <v>-21.51724138</v>
       </c>
       <c r="V48" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W48">
         <v>-0.01308</v>
@@ -18233,10 +18272,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C49" s="2">
         <v>43905.42497346065</v>
@@ -18254,13 +18293,13 @@
         <v>1599</v>
       </c>
       <c r="H49" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I49" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="J49" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="K49">
         <v>65</v>
@@ -18284,7 +18323,7 @@
         <v>-21.48275862</v>
       </c>
       <c r="V49" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W49">
         <v>0.001189</v>
@@ -18313,10 +18352,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C50" s="2">
         <v>43905.42536865741</v>
@@ -18334,13 +18373,13 @@
         <v>1628</v>
       </c>
       <c r="H50" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I50" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="J50" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="K50">
         <v>72</v>
@@ -18364,7 +18403,7 @@
         <v>-21.51724138</v>
       </c>
       <c r="V50" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W50">
         <v>-0.001189</v>
@@ -18393,10 +18432,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C51" s="2">
         <v>43905.4257625</v>
@@ -18414,13 +18453,13 @@
         <v>1657</v>
       </c>
       <c r="H51" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I51" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="J51" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="K51">
         <v>68</v>
@@ -18444,7 +18483,7 @@
         <v>-21.72413793</v>
       </c>
       <c r="V51" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W51">
         <v>-0.007134</v>
@@ -18473,10 +18512,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C52" s="2">
         <v>43905.42615916667</v>
@@ -18494,13 +18533,13 @@
         <v>1686</v>
       </c>
       <c r="H52" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I52" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="J52" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="K52">
         <v>78</v>
@@ -18524,7 +18563,7 @@
         <v>-21.5862069</v>
       </c>
       <c r="V52" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W52">
         <v>0.004756</v>
@@ -18553,10 +18592,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C53" s="2">
         <v>43905.42701133102</v>
@@ -18574,13 +18613,13 @@
         <v>1773</v>
       </c>
       <c r="H53" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I53" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="J53" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="K53">
         <v>66</v>
@@ -18604,7 +18643,7 @@
         <v>-21.01149425</v>
       </c>
       <c r="V53" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W53">
         <v>0.006606</v>
@@ -18633,10 +18672,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C54" s="2">
         <v>43905.42740899305</v>
@@ -18654,13 +18693,13 @@
         <v>1802</v>
       </c>
       <c r="H54" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I54" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="J54" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="K54">
         <v>70</v>
@@ -18684,7 +18723,7 @@
         <v>-20.68965517</v>
       </c>
       <c r="V54" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W54">
         <v>0.011098</v>
@@ -18713,10 +18752,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C55" s="2">
         <v>43905.42778587963</v>
@@ -18734,13 +18773,13 @@
         <v>1831</v>
       </c>
       <c r="H55" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I55" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="J55" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="K55">
         <v>41</v>
@@ -18764,7 +18803,7 @@
         <v>-20.27586207</v>
       </c>
       <c r="V55" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W55">
         <v>0.014269</v>
@@ -18793,10 +18832,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C56" s="2">
         <v>43905.4281658912</v>
@@ -18814,13 +18853,13 @@
         <v>1860</v>
       </c>
       <c r="H56" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I56" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="J56" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="K56">
         <v>53</v>
@@ -18844,7 +18883,7 @@
         <v>-19</v>
       </c>
       <c r="V56" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W56">
         <v>0.043995</v>
@@ -18873,10 +18912,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C57" s="2">
         <v>43905.42855125</v>
@@ -18894,13 +18933,13 @@
         <v>1889</v>
       </c>
       <c r="H57" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I57" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="J57" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="K57">
         <v>69</v>
@@ -18924,7 +18963,7 @@
         <v>-18.79310345</v>
       </c>
       <c r="V57" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W57">
         <v>0.007134</v>
@@ -18953,10 +18992,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C58" s="2">
         <v>43905.42893336806</v>
@@ -18974,13 +19013,13 @@
         <v>1918</v>
       </c>
       <c r="H58" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I58" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="J58" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="K58">
         <v>98</v>
@@ -19004,7 +19043,7 @@
         <v>-18.31034483</v>
       </c>
       <c r="V58" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W58">
         <v>0.016647</v>
@@ -19033,10 +19072,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C59" s="2">
         <v>43905.42937478009</v>
@@ -19054,13 +19093,13 @@
         <v>1976</v>
       </c>
       <c r="H59" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I59" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="J59" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="K59">
         <v>64</v>
@@ -19084,7 +19123,7 @@
         <v>-18.39655172</v>
       </c>
       <c r="V59" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W59">
         <v>-0.001486</v>
@@ -19113,10 +19152,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C60" s="2">
         <v>43905.42975957176</v>
@@ -19134,13 +19173,13 @@
         <v>2005</v>
       </c>
       <c r="H60" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I60" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="J60" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="K60">
         <v>93</v>
@@ -19164,7 +19203,7 @@
         <v>-17.75862069</v>
       </c>
       <c r="V60" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W60">
         <v>0.021998</v>
@@ -19193,10 +19232,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C61" s="2">
         <v>43905.43052959491</v>
@@ -19214,13 +19253,13 @@
         <v>2063</v>
       </c>
       <c r="H61" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I61" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="J61" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="K61">
         <v>101</v>
@@ -19244,7 +19283,7 @@
         <v>-18.5</v>
       </c>
       <c r="V61" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W61">
         <v>-0.012782</v>
@@ -19273,10 +19312,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C62" s="2">
         <v>43905.43129665509</v>
@@ -19294,13 +19333,13 @@
         <v>2121</v>
       </c>
       <c r="H62" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I62" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="J62" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="K62">
         <v>177</v>
@@ -19324,7 +19363,7 @@
         <v>-17.48275862</v>
       </c>
       <c r="V62" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W62">
         <v>0.017539</v>
@@ -19353,10 +19392,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C63" s="2">
         <v>43905.43211053241</v>
@@ -19374,13 +19413,13 @@
         <v>2208</v>
       </c>
       <c r="H63" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I63" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="J63" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="K63">
         <v>202</v>
@@ -19404,7 +19443,7 @@
         <v>-17.98850575</v>
       </c>
       <c r="V63" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W63">
         <v>-0.005813</v>
@@ -19433,10 +19472,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C64" s="2">
         <v>43905.4324965162</v>
@@ -19454,13 +19493,13 @@
         <v>2237</v>
       </c>
       <c r="H64" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I64" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="J64" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="K64">
         <v>214</v>
@@ -19484,7 +19523,7 @@
         <v>-18.20689655</v>
       </c>
       <c r="V64" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W64">
         <v>-0.007531</v>
@@ -19513,10 +19552,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C65" s="2">
         <v>43905.43288127315</v>
@@ -19534,13 +19573,13 @@
         <v>2266</v>
       </c>
       <c r="H65" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I65" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="J65" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="K65">
         <v>160</v>
@@ -19564,7 +19603,7 @@
         <v>-17.31034483</v>
       </c>
       <c r="V65" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W65">
         <v>0.030916</v>
@@ -19593,10 +19632,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C66" s="2">
         <v>43905.43325335648</v>
@@ -19614,13 +19653,13 @@
         <v>2295</v>
       </c>
       <c r="H66" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I66" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="J66" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="K66">
         <v>161</v>
@@ -19644,7 +19683,7 @@
         <v>-18.20689655</v>
       </c>
       <c r="V66" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W66">
         <v>-0.030916</v>
@@ -19673,10 +19712,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C67" s="2">
         <v>43905.43409900463</v>
@@ -19694,13 +19733,13 @@
         <v>2382</v>
       </c>
       <c r="H67" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I67" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="J67" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="K67">
         <v>66</v>
@@ -19724,7 +19763,7 @@
         <v>-17.8045977</v>
       </c>
       <c r="V67" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W67">
         <v>0.004624</v>
@@ -19753,10 +19792,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C68" s="2">
         <v>43905.43447773148</v>
@@ -19774,13 +19813,13 @@
         <v>2411</v>
       </c>
       <c r="H68" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I68" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="J68" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K68">
         <v>9</v>
@@ -19804,7 +19843,7 @@
         <v>-16.86206897</v>
       </c>
       <c r="V68" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W68">
         <v>0.032501</v>
@@ -19833,10 +19872,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C69" s="2">
         <v>43905.43486143518</v>
@@ -19854,13 +19893,13 @@
         <v>2440</v>
       </c>
       <c r="H69" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I69" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="J69" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="K69">
         <v>13</v>
@@ -19884,7 +19923,7 @@
         <v>-17.65517241</v>
       </c>
       <c r="V69" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W69">
         <v>-0.027348</v>
@@ -19913,10 +19952,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C70" s="2">
         <v>43905.43563552084</v>
@@ -19934,13 +19973,13 @@
         <v>2498</v>
       </c>
       <c r="H70" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I70" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="J70" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K70">
         <v>8</v>
@@ -19964,7 +20003,7 @@
         <v>-16.9137931</v>
       </c>
       <c r="V70" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W70">
         <v>0.012782</v>
@@ -19993,10 +20032,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C71" s="2">
         <v>43905.4360971875</v>
@@ -20014,13 +20053,13 @@
         <v>2556</v>
       </c>
       <c r="H71" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I71" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="J71" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="K71">
         <v>356</v>
@@ -20044,7 +20083,7 @@
         <v>-9.448275860000001</v>
       </c>
       <c r="V71" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="W71">
         <v>0.128716</v>

--- a/www/flightdata/xlsx/eoss-297.xlsx
+++ b/www/flightdata/xlsx/eoss-297.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="527">
   <si>
     <t>flight</t>
   </si>
@@ -228,6 +228,9 @@
     <t>velocity_curvefit</t>
   </si>
   <si>
+    <t>reynolds_transition</t>
+  </si>
+  <si>
     <t>K0SCC-14</t>
   </si>
   <si>
@@ -1165,6 +1168,9 @@
   </si>
   <si>
     <t>low Re</t>
+  </si>
+  <si>
+    <t>high_to_low</t>
   </si>
   <si>
     <t>descending</t>
@@ -2116,10 +2122,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE155"/>
+  <dimension ref="A1:AF155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -2213,13 +2219,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2">
         <v>43905.35455440972</v>
@@ -2237,13 +2246,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K2">
         <v>193</v>
@@ -2270,7 +2279,7 @@
         <v>7.79310345</v>
       </c>
       <c r="W2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y2">
         <v>7.793103</v>
@@ -2279,12 +2288,12 @@
         <v>12.906104</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2">
         <v>43905.35454506944</v>
@@ -2302,13 +2311,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K3">
         <v>228</v>
@@ -2335,7 +2344,7 @@
         <v>19.63333333</v>
       </c>
       <c r="W3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X3">
         <v>0.394674</v>
@@ -2356,12 +2365,12 @@
         <v>16.345009</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2">
         <v>43905.35493925926</v>
@@ -2379,13 +2388,13 @@
         <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K4">
         <v>265</v>
@@ -2412,7 +2421,7 @@
         <v>21.72413793</v>
       </c>
       <c r="W4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X4">
         <v>0.07209699999999999</v>
@@ -2439,12 +2448,12 @@
         <v>18.38232</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2">
         <v>43905.3548868287</v>
@@ -2462,13 +2471,13 @@
         <v>43</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K5">
         <v>12</v>
@@ -2495,7 +2504,7 @@
         <v>20.23333333</v>
       </c>
       <c r="W5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X5">
         <v>-0.049693</v>
@@ -2522,12 +2531,12 @@
         <v>20.063358</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2">
         <v>43905.35533289352</v>
@@ -2545,13 +2554,13 @@
         <v>58</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K6">
         <v>74</v>
@@ -2578,7 +2587,7 @@
         <v>21.72413793</v>
       </c>
       <c r="W6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X6">
         <v>0.051407</v>
@@ -2605,12 +2614,12 @@
         <v>21.121431</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2">
         <v>43905.35523523148</v>
@@ -2628,13 +2637,13 @@
         <v>73</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K7">
         <v>311</v>
@@ -2661,7 +2670,7 @@
         <v>22.8</v>
       </c>
       <c r="W7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X7">
         <v>0.035862</v>
@@ -2688,12 +2697,12 @@
         <v>21.898008</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2">
         <v>43905.35540681713</v>
@@ -2711,13 +2720,13 @@
         <v>87</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K8">
         <v>352</v>
@@ -2744,7 +2753,7 @@
         <v>23.4137931</v>
       </c>
       <c r="W8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X8">
         <v>0.021165</v>
@@ -2771,12 +2780,12 @@
         <v>22.193125</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2">
         <v>43905.35558158565</v>
@@ -2794,13 +2803,13 @@
         <v>103</v>
       </c>
       <c r="H9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -2827,7 +2836,7 @@
         <v>21.53333333</v>
       </c>
       <c r="W9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X9">
         <v>-0.062682</v>
@@ -2854,12 +2863,12 @@
         <v>22.279482</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2">
         <v>43905.35580268518</v>
@@ -2877,13 +2886,13 @@
         <v>116</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K10">
         <v>34</v>
@@ -2910,7 +2919,7 @@
         <v>20.93103448</v>
       </c>
       <c r="W10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X10">
         <v>-0.020769</v>
@@ -2937,12 +2946,12 @@
         <v>22.213975</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" s="2">
         <v>43905.35592921296</v>
@@ -2960,13 +2969,13 @@
         <v>133</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K11">
         <v>16</v>
@@ -2993,7 +3002,7 @@
         <v>20</v>
       </c>
       <c r="W11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X11">
         <v>-0.031034</v>
@@ -3020,12 +3029,12 @@
         <v>22.0148</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" s="2">
         <v>43905.35619954861</v>
@@ -3043,13 +3052,13 @@
         <v>145</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K12">
         <v>27</v>
@@ -3076,7 +3085,7 @@
         <v>20.03448276</v>
       </c>
       <c r="W12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X12">
         <v>0.001189</v>
@@ -3103,12 +3112,12 @@
         <v>21.820418</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="2">
         <v>43905.35627532408</v>
@@ -3126,13 +3135,13 @@
         <v>163</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -3159,7 +3168,7 @@
         <v>22.13333333</v>
       </c>
       <c r="W13" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X13">
         <v>0.069962</v>
@@ -3186,12 +3195,12 @@
         <v>21.427162</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="2">
         <v>43905.35658402778</v>
@@ -3209,13 +3218,13 @@
         <v>174</v>
       </c>
       <c r="H14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K14">
         <v>4</v>
@@ -3242,7 +3251,7 @@
         <v>21.51724138</v>
       </c>
       <c r="W14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X14">
         <v>-0.021245</v>
@@ -3269,12 +3278,12 @@
         <v>21.229512</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" s="2">
         <v>43905.35662277778</v>
@@ -3292,13 +3301,13 @@
         <v>193</v>
       </c>
       <c r="H15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K15">
         <v>43</v>
@@ -3325,7 +3334,7 @@
         <v>20.23333333</v>
       </c>
       <c r="W15" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X15">
         <v>-0.042797</v>
@@ -3352,12 +3361,12 @@
         <v>20.840887</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" s="2">
         <v>43905.35698546296</v>
@@ -3375,13 +3384,13 @@
         <v>203</v>
       </c>
       <c r="H16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K16">
         <v>353</v>
@@ -3408,7 +3417,7 @@
         <v>20.24137931</v>
       </c>
       <c r="W16" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X16">
         <v>0.000277</v>
@@ -3440,7 +3449,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" s="2">
         <v>43905.35697372686</v>
@@ -3458,13 +3467,13 @@
         <v>223</v>
       </c>
       <c r="H17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K17">
         <v>358</v>
@@ -3491,7 +3500,7 @@
         <v>20</v>
       </c>
       <c r="W17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X17">
         <v>-0.008045999999999999</v>
@@ -3523,7 +3532,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="2">
         <v>43905.3573178125</v>
@@ -3541,13 +3550,13 @@
         <v>253</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K18">
         <v>67</v>
@@ -3574,7 +3583,7 @@
         <v>18.76666667</v>
       </c>
       <c r="W18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X18">
         <v>-0.041111</v>
@@ -3606,7 +3615,7 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="2">
         <v>43905.35744141204</v>
@@ -3624,13 +3633,13 @@
         <v>261</v>
       </c>
       <c r="H19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K19">
         <v>7</v>
@@ -3657,7 +3666,7 @@
         <v>19.12068966</v>
       </c>
       <c r="W19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X19">
         <v>0.006104</v>
@@ -3689,7 +3698,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" s="2">
         <v>43905.35766472222</v>
@@ -3707,13 +3716,13 @@
         <v>283</v>
       </c>
       <c r="H20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K20">
         <v>11</v>
@@ -3740,7 +3749,7 @@
         <v>19.36666667</v>
       </c>
       <c r="W20" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X20">
         <v>0.008199</v>
@@ -3772,7 +3781,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="2">
         <v>43905.35783949074</v>
@@ -3790,13 +3799,13 @@
         <v>290</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J21" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K21">
         <v>32</v>
@@ -3823,7 +3832,7 @@
         <v>19.89655172</v>
       </c>
       <c r="W21" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X21">
         <v>0.018272</v>
@@ -3855,7 +3864,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="2">
         <v>43905.35801684028</v>
@@ -3873,13 +3882,13 @@
         <v>313</v>
       </c>
       <c r="H22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K22">
         <v>349</v>
@@ -3906,7 +3915,7 @@
         <v>20</v>
       </c>
       <c r="W22" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X22">
         <v>0.003448</v>
@@ -3938,7 +3947,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C23" s="2">
         <v>43905.35822041667</v>
@@ -3956,13 +3965,13 @@
         <v>319</v>
       </c>
       <c r="H23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K23">
         <v>38</v>
@@ -3989,7 +3998,7 @@
         <v>20.03448276</v>
       </c>
       <c r="W23" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X23">
         <v>0.001189</v>
@@ -4021,7 +4030,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C24" s="2">
         <v>43905.35835924769</v>
@@ -4039,13 +4048,13 @@
         <v>343</v>
       </c>
       <c r="H24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J24" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K24">
         <v>333</v>
@@ -4072,7 +4081,7 @@
         <v>19.73333333</v>
       </c>
       <c r="W24" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X24">
         <v>-0.010038</v>
@@ -4104,7 +4113,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="2">
         <v>43905.3586212037</v>
@@ -4122,13 +4131,13 @@
         <v>348</v>
       </c>
       <c r="H25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J25" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K25">
         <v>315</v>
@@ -4155,7 +4164,7 @@
         <v>19.48275862</v>
       </c>
       <c r="W25" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X25">
         <v>-0.008640999999999999</v>
@@ -4187,7 +4196,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C26" s="2">
         <v>43905.35870618055</v>
@@ -4205,13 +4214,13 @@
         <v>373</v>
       </c>
       <c r="H26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J26" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K26">
         <v>10</v>
@@ -4238,7 +4247,7 @@
         <v>20.33333333</v>
       </c>
       <c r="W26" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X26">
         <v>0.028352</v>
@@ -4270,7 +4279,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="2">
         <v>43905.35901060185</v>
@@ -4288,13 +4297,13 @@
         <v>377</v>
       </c>
       <c r="H27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J27" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K27">
         <v>33</v>
@@ -4321,7 +4330,7 @@
         <v>20.93103448</v>
       </c>
       <c r="W27" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X27">
         <v>0.02061</v>
@@ -4353,7 +4362,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="2">
         <v>43905.35905450232</v>
@@ -4371,13 +4380,13 @@
         <v>403</v>
       </c>
       <c r="H28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J28" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K28">
         <v>2</v>
@@ -4404,7 +4413,7 @@
         <v>21.13333333</v>
       </c>
       <c r="W28" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X28">
         <v>0.006743</v>
@@ -4436,7 +4445,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="2">
         <v>43905.35940105324</v>
@@ -4454,13 +4463,13 @@
         <v>433</v>
       </c>
       <c r="H29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J29" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K29">
         <v>42</v>
@@ -4487,7 +4496,7 @@
         <v>20.26666667</v>
       </c>
       <c r="W29" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X29">
         <v>-0.028889</v>
@@ -4519,7 +4528,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" s="2">
         <v>43905.35946864583</v>
@@ -4537,13 +4546,13 @@
         <v>435</v>
       </c>
       <c r="H30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J30" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K30">
         <v>48</v>
@@ -4570,7 +4579,7 @@
         <v>20.75862069</v>
       </c>
       <c r="W30" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X30">
         <v>0.008482</v>
@@ -4602,7 +4611,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2">
         <v>43905.35974765047</v>
@@ -4620,13 +4629,13 @@
         <v>463</v>
       </c>
       <c r="H31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J31" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K31">
         <v>67</v>
@@ -4653,7 +4662,7 @@
         <v>23.03333333</v>
       </c>
       <c r="W31" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X31">
         <v>0.075824</v>
@@ -4685,7 +4694,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2">
         <v>43905.36009555555</v>
@@ -4703,13 +4712,13 @@
         <v>493</v>
       </c>
       <c r="H32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J32" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K32">
         <v>59</v>
@@ -4736,7 +4745,7 @@
         <v>21.7</v>
       </c>
       <c r="W32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X32">
         <v>-0.044444</v>
@@ -4768,7 +4777,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" s="2">
         <v>43905.36025887731</v>
@@ -4786,13 +4795,13 @@
         <v>493</v>
       </c>
       <c r="H33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K33">
         <v>65</v>
@@ -4819,7 +4828,7 @@
         <v>22.39655172</v>
       </c>
       <c r="W33" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X33">
         <v>0.01201</v>
@@ -4851,7 +4860,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C34" s="2">
         <v>43905.36064675926</v>
@@ -4869,13 +4878,13 @@
         <v>522</v>
       </c>
       <c r="H34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J34" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K34">
         <v>72</v>
@@ -4902,7 +4911,7 @@
         <v>18.68965517</v>
       </c>
       <c r="W34" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X34">
         <v>-0.127824</v>
@@ -4934,7 +4943,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" s="2">
         <v>43905.36044202546</v>
@@ -4952,13 +4961,13 @@
         <v>523</v>
       </c>
       <c r="H35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J35" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K35">
         <v>62</v>
@@ -4985,7 +4994,7 @@
         <v>19</v>
       </c>
       <c r="W35" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X35">
         <v>0.010345</v>
@@ -5017,7 +5026,7 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C36" s="2">
         <v>43905.36079018519</v>
@@ -5035,13 +5044,13 @@
         <v>553</v>
       </c>
       <c r="H36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J36" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K36">
         <v>64</v>
@@ -5068,7 +5077,7 @@
         <v>18.8</v>
       </c>
       <c r="W36" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X36">
         <v>-0.006667</v>
@@ -5100,7 +5109,7 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C37" s="2">
         <v>43905.36111953704</v>
@@ -5118,13 +5127,13 @@
         <v>580</v>
       </c>
       <c r="H37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J37" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K37">
         <v>78</v>
@@ -5151,7 +5160,7 @@
         <v>19.84482759</v>
       </c>
       <c r="W37" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X37">
         <v>0.018014</v>
@@ -5183,7 +5192,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2">
         <v>43905.36113657407</v>
@@ -5201,13 +5210,13 @@
         <v>583</v>
       </c>
       <c r="H38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J38" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K38">
         <v>61</v>
@@ -5234,7 +5243,7 @@
         <v>21.1</v>
       </c>
       <c r="W38" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X38">
         <v>0.041839</v>
@@ -5266,7 +5275,7 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C39" s="2">
         <v>43905.36150556713</v>
@@ -5284,13 +5293,13 @@
         <v>609</v>
       </c>
       <c r="H39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J39" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K39">
         <v>46</v>
@@ -5317,7 +5326,7 @@
         <v>21.96551724</v>
       </c>
       <c r="W39" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X39">
         <v>0.029845</v>
@@ -5349,7 +5358,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C40" s="2">
         <v>43905.36148440972</v>
@@ -5367,13 +5376,13 @@
         <v>613</v>
       </c>
       <c r="H40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J40" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K40">
         <v>64</v>
@@ -5400,7 +5409,7 @@
         <v>21.73333333</v>
       </c>
       <c r="W40" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X40">
         <v>-0.007739</v>
@@ -5432,7 +5441,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C41" s="2">
         <v>43905.36190732639</v>
@@ -5450,13 +5459,13 @@
         <v>638</v>
       </c>
       <c r="H41" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J41" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K41">
         <v>64</v>
@@ -5483,7 +5492,7 @@
         <v>18.65517241</v>
       </c>
       <c r="W41" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X41">
         <v>-0.106143</v>
@@ -5515,7 +5524,7 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42" s="2">
         <v>43905.36183105324</v>
@@ -5533,13 +5542,13 @@
         <v>643</v>
       </c>
       <c r="H42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J42" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K42">
         <v>48</v>
@@ -5566,7 +5575,7 @@
         <v>18.8</v>
       </c>
       <c r="W42" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X42">
         <v>0.004828</v>
@@ -5598,7 +5607,7 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C43" s="2">
         <v>43905.3623027662</v>
@@ -5616,13 +5625,13 @@
         <v>667</v>
       </c>
       <c r="H43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J43" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K43">
         <v>47</v>
@@ -5649,7 +5658,7 @@
         <v>18.44827586</v>
       </c>
       <c r="W43" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X43">
         <v>-0.012128</v>
@@ -5681,7 +5690,7 @@
         <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C44" s="2">
         <v>43905.36217925926</v>
@@ -5699,13 +5708,13 @@
         <v>673</v>
       </c>
       <c r="H44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J44" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K44">
         <v>52</v>
@@ -5732,7 +5741,7 @@
         <v>18.03333333</v>
       </c>
       <c r="W44" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X44">
         <v>-0.013831</v>
@@ -5764,7 +5773,7 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C45" s="2">
         <v>43905.36270061343</v>
@@ -5782,13 +5791,13 @@
         <v>696</v>
       </c>
       <c r="H45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J45" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K45">
         <v>52</v>
@@ -5815,7 +5824,7 @@
         <v>18.20689655</v>
       </c>
       <c r="W45" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X45">
         <v>0.005985</v>
@@ -5847,7 +5856,7 @@
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C46" s="2">
         <v>43905.36252603009</v>
@@ -5865,13 +5874,13 @@
         <v>703</v>
       </c>
       <c r="H46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J46" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K46">
         <v>44</v>
@@ -5898,7 +5907,7 @@
         <v>18.4</v>
       </c>
       <c r="W46" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X46">
         <v>0.006437</v>
@@ -5930,7 +5939,7 @@
         <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C47" s="2">
         <v>43905.36287436343</v>
@@ -5948,13 +5957,13 @@
         <v>733</v>
       </c>
       <c r="H47" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J47" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K47">
         <v>68</v>
@@ -5981,7 +5990,7 @@
         <v>21.83333333</v>
       </c>
       <c r="W47" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X47">
         <v>0.114444</v>
@@ -6013,7 +6022,7 @@
         <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C48" s="2">
         <v>43905.36314751158</v>
@@ -6031,13 +6040,13 @@
         <v>754</v>
       </c>
       <c r="H48" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J48" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K48">
         <v>79</v>
@@ -6064,7 +6073,7 @@
         <v>21.17241379</v>
       </c>
       <c r="W48" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X48">
         <v>-0.011395</v>
@@ -6096,7 +6105,7 @@
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C49" s="2">
         <v>43905.36322112269</v>
@@ -6114,13 +6123,13 @@
         <v>763</v>
       </c>
       <c r="H49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J49" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K49">
         <v>68</v>
@@ -6147,7 +6156,7 @@
         <v>18.4</v>
       </c>
       <c r="W49" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X49">
         <v>-0.092414</v>
@@ -6179,7 +6188,7 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C50" s="2">
         <v>43905.36354105324</v>
@@ -6197,13 +6206,13 @@
         <v>783</v>
       </c>
       <c r="H50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J50" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K50">
         <v>84</v>
@@ -6230,7 +6239,7 @@
         <v>20.13793103</v>
       </c>
       <c r="W50" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X50">
         <v>0.059929</v>
@@ -6262,7 +6271,7 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C51" s="2">
         <v>43905.36356884259</v>
@@ -6280,13 +6289,13 @@
         <v>793</v>
       </c>
       <c r="H51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I51" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J51" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K51">
         <v>75</v>
@@ -6313,7 +6322,7 @@
         <v>22.33333333</v>
       </c>
       <c r="W51" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X51">
         <v>0.07318</v>
@@ -6345,7 +6354,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C52" s="2">
         <v>43905.36394129629</v>
@@ -6363,13 +6372,13 @@
         <v>812</v>
       </c>
       <c r="H52" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I52" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J52" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K52">
         <v>72</v>
@@ -6396,7 +6405,7 @@
         <v>21.72413793</v>
       </c>
       <c r="W52" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X52">
         <v>-0.021007</v>
@@ -6428,7 +6437,7 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C53" s="2">
         <v>43905.36391539352</v>
@@ -6446,13 +6455,13 @@
         <v>823</v>
       </c>
       <c r="H53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I53" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J53" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K53">
         <v>66</v>
@@ -6479,7 +6488,7 @@
         <v>21.73333333</v>
       </c>
       <c r="W53" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X53">
         <v>0.000307</v>
@@ -6511,7 +6520,7 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C54" s="2">
         <v>43905.36433449074</v>
@@ -6529,13 +6538,13 @@
         <v>841</v>
       </c>
       <c r="H54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I54" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J54" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K54">
         <v>62</v>
@@ -6562,7 +6571,7 @@
         <v>21.27586207</v>
       </c>
       <c r="W54" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X54">
         <v>-0.015775</v>
@@ -6594,7 +6603,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2">
         <v>43905.36426375</v>
@@ -6612,13 +6621,13 @@
         <v>853</v>
       </c>
       <c r="H55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J55" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K55">
         <v>65</v>
@@ -6645,7 +6654,7 @@
         <v>21.03333333</v>
       </c>
       <c r="W55" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X55">
         <v>-0.008083999999999999</v>
@@ -6677,7 +6686,7 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C56" s="2">
         <v>43905.36460951389</v>
@@ -6695,13 +6704,13 @@
         <v>883</v>
       </c>
       <c r="H56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J56" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K56">
         <v>82</v>
@@ -6728,7 +6737,7 @@
         <v>25.2</v>
       </c>
       <c r="W56" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X56">
         <v>0.138889</v>
@@ -6760,7 +6769,7 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C57" s="2">
         <v>43905.36495675926</v>
@@ -6778,13 +6787,13 @@
         <v>913</v>
       </c>
       <c r="H57" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J57" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K57">
         <v>77</v>
@@ -6811,7 +6820,7 @@
         <v>21.8</v>
       </c>
       <c r="W57" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X57">
         <v>-0.113333</v>
@@ -6843,7 +6852,7 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C58" s="2">
         <v>43905.36518355324</v>
@@ -6861,13 +6870,13 @@
         <v>928</v>
       </c>
       <c r="H58" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I58" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J58" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K58">
         <v>69</v>
@@ -6894,7 +6903,7 @@
         <v>22.81609195</v>
       </c>
       <c r="W58" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X58">
         <v>0.011679</v>
@@ -6926,7 +6935,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C59" s="2">
         <v>43905.36530372685</v>
@@ -6944,13 +6953,13 @@
         <v>943</v>
       </c>
       <c r="H59" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J59" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K59">
         <v>65</v>
@@ -6977,7 +6986,7 @@
         <v>22.63333333</v>
       </c>
       <c r="W59" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X59">
         <v>-0.006092</v>
@@ -7009,7 +7018,7 @@
         <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C60" s="2">
         <v>43905.36558168982</v>
@@ -7027,13 +7036,13 @@
         <v>957</v>
       </c>
       <c r="H60" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J60" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K60">
         <v>75</v>
@@ -7060,7 +7069,7 @@
         <v>23.06896552</v>
       </c>
       <c r="W60" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X60">
         <v>0.015022</v>
@@ -7092,7 +7101,7 @@
         <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C61" s="2">
         <v>43905.36565145833</v>
@@ -7110,13 +7119,13 @@
         <v>973</v>
       </c>
       <c r="H61" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J61" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K61">
         <v>69</v>
@@ -7143,7 +7152,7 @@
         <v>22.33333333</v>
       </c>
       <c r="W61" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X61">
         <v>-0.024521</v>
@@ -7175,7 +7184,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C62" s="2">
         <v>43905.36597920139</v>
@@ -7193,13 +7202,13 @@
         <v>986</v>
       </c>
       <c r="H62" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J62" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K62">
         <v>71</v>
@@ -7226,7 +7235,7 @@
         <v>22.17241379</v>
       </c>
       <c r="W62" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X62">
         <v>-0.005549</v>
@@ -7258,7 +7267,7 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C63" s="2">
         <v>43905.36600150463</v>
@@ -7276,13 +7285,13 @@
         <v>1003</v>
       </c>
       <c r="H63" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J63" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K63">
         <v>64</v>
@@ -7309,7 +7318,7 @@
         <v>24.73333333</v>
       </c>
       <c r="W63" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X63">
         <v>0.085364</v>
@@ -7341,7 +7350,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64" s="2">
         <v>43905.3663808912</v>
@@ -7359,13 +7368,13 @@
         <v>1015</v>
       </c>
       <c r="H64" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J64" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K64">
         <v>61</v>
@@ -7392,7 +7401,7 @@
         <v>22.65517241</v>
       </c>
       <c r="W64" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X64">
         <v>-0.071661</v>
@@ -7419,12 +7428,12 @@
         <v>21.984842</v>
       </c>
     </row>
-    <row r="65" spans="1:31">
+    <row r="65" spans="1:32">
       <c r="A65" t="s">
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="2">
         <v>43905.36634446759</v>
@@ -7442,13 +7451,13 @@
         <v>1033</v>
       </c>
       <c r="H65" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J65" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K65">
         <v>64</v>
@@ -7475,7 +7484,7 @@
         <v>18.06666667</v>
       </c>
       <c r="W65" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X65">
         <v>-0.15295</v>
@@ -7502,12 +7511,12 @@
         <v>22.020823</v>
       </c>
     </row>
-    <row r="66" spans="1:31">
+    <row r="66" spans="1:32">
       <c r="A66" t="s">
         <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C66" s="2">
         <v>43905.36669266204</v>
@@ -7525,13 +7534,13 @@
         <v>1063</v>
       </c>
       <c r="H66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J66" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K66">
         <v>76</v>
@@ -7558,7 +7567,7 @@
         <v>19.26666667</v>
       </c>
       <c r="W66" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X66">
         <v>0.04</v>
@@ -7585,12 +7594,12 @@
         <v>22.052831</v>
       </c>
     </row>
-    <row r="67" spans="1:31">
+    <row r="67" spans="1:32">
       <c r="A67" t="s">
         <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C67" s="2">
         <v>43905.36685060185</v>
@@ -7608,13 +7617,13 @@
         <v>1073</v>
       </c>
       <c r="H67" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I67" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J67" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K67">
         <v>70</v>
@@ -7641,7 +7650,7 @@
         <v>20.98275862</v>
       </c>
       <c r="W67" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X67">
         <v>0.029588</v>
@@ -7668,12 +7677,12 @@
         <v>22.053021</v>
       </c>
     </row>
-    <row r="68" spans="1:31">
+    <row r="68" spans="1:32">
       <c r="A68" t="s">
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C68" s="2">
         <v>43905.36704002315</v>
@@ -7691,13 +7700,13 @@
         <v>1093</v>
       </c>
       <c r="H68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I68" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J68" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K68">
         <v>58</v>
@@ -7724,7 +7733,7 @@
         <v>25.8</v>
       </c>
       <c r="W68" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X68">
         <v>0.160575</v>
@@ -7751,12 +7760,12 @@
         <v>22.028182</v>
       </c>
     </row>
-    <row r="69" spans="1:31">
+    <row r="69" spans="1:32">
       <c r="A69" t="s">
         <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C69" s="2">
         <v>43905.36726461806</v>
@@ -7774,13 +7783,13 @@
         <v>1102</v>
       </c>
       <c r="H69" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I69" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J69" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K69">
         <v>70</v>
@@ -7807,7 +7816,7 @@
         <v>24.75862069</v>
       </c>
       <c r="W69" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X69">
         <v>-0.03591</v>
@@ -7834,12 +7843,12 @@
         <v>22.002519</v>
       </c>
     </row>
-    <row r="70" spans="1:31">
+    <row r="70" spans="1:32">
       <c r="A70" t="s">
         <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C70" s="2">
         <v>43905.36767171296</v>
@@ -7857,13 +7866,13 @@
         <v>1131</v>
       </c>
       <c r="H70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I70" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J70" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K70">
         <v>76</v>
@@ -7890,7 +7899,7 @@
         <v>24.24137931</v>
       </c>
       <c r="W70" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X70">
         <v>-0.017836</v>
@@ -7917,12 +7926,12 @@
         <v>21.877404</v>
       </c>
     </row>
-    <row r="71" spans="1:31">
+    <row r="71" spans="1:32">
       <c r="A71" t="s">
         <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C71" s="2">
         <v>43905.36773390046</v>
@@ -7940,13 +7949,13 @@
         <v>1153</v>
       </c>
       <c r="H71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I71" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J71" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K71">
         <v>67</v>
@@ -7973,7 +7982,7 @@
         <v>19.21666667</v>
       </c>
       <c r="W71" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X71">
         <v>-0.083745</v>
@@ -8000,12 +8009,12 @@
         <v>21.826051</v>
       </c>
     </row>
-    <row r="72" spans="1:31">
+    <row r="72" spans="1:32">
       <c r="A72" t="s">
         <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C72" s="2">
         <v>43905.36895555555</v>
@@ -8023,13 +8032,13 @@
         <v>1247</v>
       </c>
       <c r="H72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I72" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J72" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K72">
         <v>66</v>
@@ -8056,7 +8065,7 @@
         <v>21.26724138</v>
       </c>
       <c r="W72" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X72">
         <v>0.017677</v>
@@ -8083,12 +8092,12 @@
         <v>20.808252</v>
       </c>
     </row>
-    <row r="73" spans="1:31">
+    <row r="73" spans="1:32">
       <c r="A73" t="s">
         <v>25</v>
       </c>
       <c r="B73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C73" s="2">
         <v>43905.36935763889</v>
@@ -8106,13 +8115,13 @@
         <v>1276</v>
       </c>
       <c r="H73" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I73" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J73" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K73">
         <v>71</v>
@@ -8139,7 +8148,7 @@
         <v>21.82758621</v>
       </c>
       <c r="W73" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X73">
         <v>0.019322</v>
@@ -8166,12 +8175,12 @@
         <v>20.386247</v>
       </c>
     </row>
-    <row r="74" spans="1:31">
+    <row r="74" spans="1:32">
       <c r="A74" t="s">
         <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C74" s="2">
         <v>43905.36975553241</v>
@@ -8189,13 +8198,13 @@
         <v>1305</v>
       </c>
       <c r="H74" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I74" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J74" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K74">
         <v>64</v>
@@ -8222,7 +8231,7 @@
         <v>18.89655172</v>
       </c>
       <c r="W74" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X74">
         <v>-0.10107</v>
@@ -8248,13 +8257,16 @@
       <c r="AE74">
         <v>19.981292</v>
       </c>
-    </row>
-    <row r="75" spans="1:31">
+      <c r="AF74" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="75" spans="1:32">
       <c r="A75" t="s">
         <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C75" s="2">
         <v>43905.37023015046</v>
@@ -8272,13 +8284,13 @@
         <v>1363</v>
       </c>
       <c r="H75" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I75" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J75" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K75">
         <v>60</v>
@@ -8305,7 +8317,7 @@
         <v>17.25862069</v>
       </c>
       <c r="W75" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X75">
         <v>-0.02824</v>
@@ -8332,12 +8344,12 @@
         <v>19.1673</v>
       </c>
     </row>
-    <row r="76" spans="1:31">
+    <row r="76" spans="1:32">
       <c r="A76" t="s">
         <v>25</v>
       </c>
       <c r="B76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C76" s="2">
         <v>43905.37062890046</v>
@@ -8355,13 +8367,13 @@
         <v>1392</v>
       </c>
       <c r="H76" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I76" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J76" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K76">
         <v>67</v>
@@ -8388,7 +8400,7 @@
         <v>18.20689655</v>
       </c>
       <c r="W76" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X76">
         <v>0.032699</v>
@@ -8415,12 +8427,12 @@
         <v>18.71112</v>
       </c>
     </row>
-    <row r="77" spans="1:31">
+    <row r="77" spans="1:32">
       <c r="A77" t="s">
         <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C77" s="2">
         <v>43905.37102997685</v>
@@ -8438,13 +8450,13 @@
         <v>1421</v>
       </c>
       <c r="H77" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I77" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J77" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K77">
         <v>68</v>
@@ -8471,7 +8483,7 @@
         <v>11.65517241</v>
       </c>
       <c r="W77" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X77">
         <v>-0.225922</v>
@@ -8498,12 +8510,12 @@
         <v>18.413589</v>
       </c>
     </row>
-    <row r="78" spans="1:31">
+    <row r="78" spans="1:32">
       <c r="A78" t="s">
         <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C78" s="2">
         <v>43905.37142820602</v>
@@ -8521,13 +8533,13 @@
         <v>1450</v>
       </c>
       <c r="H78" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I78" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J78" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K78">
         <v>63</v>
@@ -8554,7 +8566,7 @@
         <v>11.10344828</v>
       </c>
       <c r="W78" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X78">
         <v>-0.019025</v>
@@ -8581,12 +8593,12 @@
         <v>18.128193</v>
       </c>
     </row>
-    <row r="79" spans="1:31">
+    <row r="79" spans="1:32">
       <c r="A79" t="s">
         <v>25</v>
       </c>
       <c r="B79" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C79" s="2">
         <v>43905.37189575232</v>
@@ -8604,13 +8616,13 @@
         <v>1508</v>
       </c>
       <c r="H79" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I79" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J79" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K79">
         <v>65</v>
@@ -8637,7 +8649,7 @@
         <v>13.29310345</v>
       </c>
       <c r="W79" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X79">
         <v>0.037753</v>
@@ -8664,12 +8676,12 @@
         <v>17.447072</v>
       </c>
     </row>
-    <row r="80" spans="1:31">
+    <row r="80" spans="1:32">
       <c r="A80" t="s">
         <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C80" s="2">
         <v>43905.37229842593</v>
@@ -8687,13 +8699,13 @@
         <v>1537</v>
       </c>
       <c r="H80" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I80" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J80" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K80">
         <v>72</v>
@@ -8720,7 +8732,7 @@
         <v>14.37931034</v>
       </c>
       <c r="W80" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X80">
         <v>0.037455</v>
@@ -8752,7 +8764,7 @@
         <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C81" s="2">
         <v>43905.37270165509</v>
@@ -8770,13 +8782,13 @@
         <v>1566</v>
       </c>
       <c r="H81" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I81" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J81" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K81">
         <v>66</v>
@@ -8803,7 +8815,7 @@
         <v>22.51724138</v>
       </c>
       <c r="W81" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X81">
         <v>0.280618</v>
@@ -8835,7 +8847,7 @@
         <v>25</v>
       </c>
       <c r="B82" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C82" s="2">
         <v>43905.37310010417</v>
@@ -8853,13 +8865,13 @@
         <v>1595</v>
       </c>
       <c r="H82" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I82" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J82" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K82">
         <v>66</v>
@@ -8886,7 +8898,7 @@
         <v>18.20689655</v>
       </c>
       <c r="W82" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X82">
         <v>-0.148633</v>
@@ -8918,7 +8930,7 @@
         <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C83" s="2">
         <v>43905.37357592593</v>
@@ -8936,13 +8948,13 @@
         <v>1653</v>
       </c>
       <c r="H83" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I83" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J83" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K83">
         <v>56</v>
@@ -8969,7 +8981,7 @@
         <v>18.62068966</v>
       </c>
       <c r="W83" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X83">
         <v>0.007134</v>
@@ -9001,7 +9013,7 @@
         <v>25</v>
       </c>
       <c r="B84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C84" s="2">
         <v>43905.37397979166</v>
@@ -9019,13 +9031,13 @@
         <v>1682</v>
       </c>
       <c r="H84" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I84" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J84" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K84">
         <v>72</v>
@@ -9052,7 +9064,7 @@
         <v>18.75862069</v>
       </c>
       <c r="W84" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X84">
         <v>0.004756</v>
@@ -9084,7 +9096,7 @@
         <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C85" s="2">
         <v>43905.37437518519</v>
@@ -9102,13 +9114,13 @@
         <v>1711</v>
       </c>
       <c r="H85" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I85" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J85" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K85">
         <v>73</v>
@@ -9135,7 +9147,7 @@
         <v>15.96551724</v>
       </c>
       <c r="W85" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X85">
         <v>-0.096314</v>
@@ -9167,7 +9179,7 @@
         <v>25</v>
       </c>
       <c r="B86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C86" s="2">
         <v>43905.37477902778</v>
@@ -9185,13 +9197,13 @@
         <v>1740</v>
       </c>
       <c r="H86" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I86" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J86" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K86">
         <v>64</v>
@@ -9218,7 +9230,7 @@
         <v>19.5862069</v>
       </c>
       <c r="W86" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X86">
         <v>0.124851</v>
@@ -9250,7 +9262,7 @@
         <v>25</v>
       </c>
       <c r="B87" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C87" s="2">
         <v>43905.3753066088</v>
@@ -9268,13 +9280,13 @@
         <v>1802</v>
       </c>
       <c r="H87" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I87" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J87" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K87">
         <v>71</v>
@@ -9301,7 +9313,7 @@
         <v>12.06451613</v>
       </c>
       <c r="W87" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X87">
         <v>-0.121318</v>
@@ -9333,7 +9345,7 @@
         <v>25</v>
       </c>
       <c r="B88" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C88" s="2">
         <v>43905.37570754629</v>
@@ -9351,13 +9363,13 @@
         <v>1831</v>
       </c>
       <c r="H88" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I88" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J88" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K88">
         <v>66</v>
@@ -9384,7 +9396,7 @@
         <v>14.34482759</v>
       </c>
       <c r="W88" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X88">
         <v>0.07863100000000001</v>
@@ -9416,7 +9428,7 @@
         <v>25</v>
       </c>
       <c r="B89" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C89" s="2">
         <v>43905.37611783565</v>
@@ -9434,13 +9446,13 @@
         <v>1860</v>
       </c>
       <c r="H89" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I89" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J89" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K89">
         <v>70</v>
@@ -9467,7 +9479,7 @@
         <v>14.82758621</v>
       </c>
       <c r="W89" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X89">
         <v>0.016647</v>
@@ -9499,7 +9511,7 @@
         <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C90" s="2">
         <v>43905.37651451389</v>
@@ -9517,13 +9529,13 @@
         <v>1889</v>
       </c>
       <c r="H90" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I90" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J90" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K90">
         <v>73</v>
@@ -9550,7 +9562,7 @@
         <v>16.65517241</v>
       </c>
       <c r="W90" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X90">
         <v>0.06302000000000001</v>
@@ -9582,7 +9594,7 @@
         <v>25</v>
       </c>
       <c r="B91" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C91" s="2">
         <v>43905.376594375</v>
@@ -9600,13 +9612,13 @@
         <v>1918</v>
       </c>
       <c r="H91" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I91" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J91" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K91">
         <v>56</v>
@@ -9633,7 +9645,7 @@
         <v>16.17241379</v>
       </c>
       <c r="W91" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X91">
         <v>-0.016647</v>
@@ -9665,7 +9677,7 @@
         <v>25</v>
       </c>
       <c r="B92" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C92" s="2">
         <v>43905.37700059028</v>
@@ -9683,13 +9695,13 @@
         <v>1947</v>
       </c>
       <c r="H92" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I92" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J92" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K92">
         <v>77</v>
@@ -9716,7 +9728,7 @@
         <v>18</v>
       </c>
       <c r="W92" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X92">
         <v>0.06302000000000001</v>
@@ -9748,7 +9760,7 @@
         <v>25</v>
       </c>
       <c r="B93" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C93" s="2">
         <v>43905.37740570602</v>
@@ -9766,13 +9778,13 @@
         <v>1976</v>
       </c>
       <c r="H93" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I93" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J93" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K93">
         <v>63</v>
@@ -9799,7 +9811,7 @@
         <v>15.27586207</v>
       </c>
       <c r="W93" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X93">
         <v>-0.09393600000000001</v>
@@ -9831,7 +9843,7 @@
         <v>25</v>
       </c>
       <c r="B94" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C94" s="2">
         <v>43905.37781907408</v>
@@ -9849,13 +9861,13 @@
         <v>2005</v>
       </c>
       <c r="H94" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I94" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J94" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K94">
         <v>58</v>
@@ -9882,7 +9894,7 @@
         <v>13.44827586</v>
       </c>
       <c r="W94" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X94">
         <v>-0.06302000000000001</v>
@@ -9914,7 +9926,7 @@
         <v>25</v>
       </c>
       <c r="B95" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C95" s="2">
         <v>43905.37828546296</v>
@@ -9932,13 +9944,13 @@
         <v>2063</v>
       </c>
       <c r="H95" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I95" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J95" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K95">
         <v>62</v>
@@ -9965,7 +9977,7 @@
         <v>11.87931034</v>
       </c>
       <c r="W95" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X95">
         <v>-0.027051</v>
@@ -9997,7 +10009,7 @@
         <v>25</v>
       </c>
       <c r="B96" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C96" s="2">
         <v>43905.37868584491</v>
@@ -10015,13 +10027,13 @@
         <v>2092</v>
       </c>
       <c r="H96" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I96" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J96" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K96">
         <v>70</v>
@@ -10048,7 +10060,7 @@
         <v>14.03448276</v>
       </c>
       <c r="W96" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X96">
         <v>0.07431599999999999</v>
@@ -10080,7 +10092,7 @@
         <v>25</v>
       </c>
       <c r="B97" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C97" s="2">
         <v>43905.3790844213</v>
@@ -10098,13 +10110,13 @@
         <v>2121</v>
       </c>
       <c r="H97" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I97" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J97" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K97">
         <v>73</v>
@@ -10131,7 +10143,7 @@
         <v>15.62068966</v>
       </c>
       <c r="W97" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X97">
         <v>0.054697</v>
@@ -10163,7 +10175,7 @@
         <v>25</v>
       </c>
       <c r="B98" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C98" s="2">
         <v>43905.37949032407</v>
@@ -10181,13 +10193,13 @@
         <v>2150</v>
       </c>
       <c r="H98" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I98" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J98" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K98">
         <v>59</v>
@@ -10214,7 +10226,7 @@
         <v>17.65517241</v>
       </c>
       <c r="W98" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X98">
         <v>0.070155</v>
@@ -10246,7 +10258,7 @@
         <v>25</v>
       </c>
       <c r="B99" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C99" s="2">
         <v>43905.3799602662</v>
@@ -10264,13 +10276,13 @@
         <v>2208</v>
       </c>
       <c r="H99" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I99" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J99" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K99">
         <v>60</v>
@@ -10297,7 +10309,7 @@
         <v>17.31034483</v>
       </c>
       <c r="W99" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X99">
         <v>-0.005945</v>
@@ -10329,7 +10341,7 @@
         <v>25</v>
       </c>
       <c r="B100" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C100" s="2">
         <v>43905.38074758102</v>
@@ -10347,13 +10359,13 @@
         <v>2266</v>
       </c>
       <c r="H100" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I100" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J100" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K100">
         <v>77</v>
@@ -10380,7 +10392,7 @@
         <v>16.56896552</v>
       </c>
       <c r="W100" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X100">
         <v>-0.012782</v>
@@ -10412,7 +10424,7 @@
         <v>25</v>
       </c>
       <c r="B101" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C101" s="2">
         <v>43905.38114480324</v>
@@ -10430,13 +10442,13 @@
         <v>2295</v>
       </c>
       <c r="H101" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I101" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J101" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K101">
         <v>81</v>
@@ -10463,7 +10475,7 @@
         <v>13.24137931</v>
       </c>
       <c r="W101" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X101">
         <v>-0.114744</v>
@@ -10495,7 +10507,7 @@
         <v>25</v>
       </c>
       <c r="B102" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C102" s="2">
         <v>43905.38153673611</v>
@@ -10513,13 +10525,13 @@
         <v>2324</v>
       </c>
       <c r="H102" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I102" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J102" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K102">
         <v>79</v>
@@ -10546,7 +10558,7 @@
         <v>10.17241379</v>
       </c>
       <c r="W102" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X102">
         <v>-0.105826</v>
@@ -10578,7 +10590,7 @@
         <v>25</v>
       </c>
       <c r="B103" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C103" s="2">
         <v>43905.381996875</v>
@@ -10596,13 +10608,13 @@
         <v>2382</v>
       </c>
       <c r="H103" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I103" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J103" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K103">
         <v>74</v>
@@ -10629,7 +10641,7 @@
         <v>9.62068966</v>
       </c>
       <c r="W103" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X103">
         <v>-0.009512</v>
@@ -10661,7 +10673,7 @@
         <v>25</v>
       </c>
       <c r="B104" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C104" s="2">
         <v>43905.38239262732</v>
@@ -10679,13 +10691,13 @@
         <v>2411</v>
       </c>
       <c r="H104" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I104" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J104" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K104">
         <v>74</v>
@@ -10712,7 +10724,7 @@
         <v>11.65517241</v>
       </c>
       <c r="W104" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X104">
         <v>0.070155</v>
@@ -10744,7 +10756,7 @@
         <v>25</v>
       </c>
       <c r="B105" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C105" s="2">
         <v>43905.3831684375</v>
@@ -10762,13 +10774,13 @@
         <v>2469</v>
       </c>
       <c r="H105" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I105" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J105" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K105">
         <v>83</v>
@@ -10795,7 +10807,7 @@
         <v>15.79310345</v>
       </c>
       <c r="W105" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X105">
         <v>0.071344</v>
@@ -10827,7 +10839,7 @@
         <v>25</v>
       </c>
       <c r="B106" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C106" s="2">
         <v>43905.38355795139</v>
@@ -10845,13 +10857,13 @@
         <v>2498</v>
       </c>
       <c r="H106" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I106" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J106" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K106">
         <v>65</v>
@@ -10878,7 +10890,7 @@
         <v>19.89655172</v>
       </c>
       <c r="W106" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X106">
         <v>0.141498</v>
@@ -10910,7 +10922,7 @@
         <v>25</v>
       </c>
       <c r="B107" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C107" s="2">
         <v>43905.38401408565</v>
@@ -10928,13 +10940,13 @@
         <v>2556</v>
       </c>
       <c r="H107" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I107" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J107" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K107">
         <v>60</v>
@@ -10961,7 +10973,7 @@
         <v>20.82758621</v>
       </c>
       <c r="W107" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X107">
         <v>0.016052</v>
@@ -10993,7 +11005,7 @@
         <v>25</v>
       </c>
       <c r="B108" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C108" s="2">
         <v>43905.38478722222</v>
@@ -11011,13 +11023,13 @@
         <v>2614</v>
       </c>
       <c r="H108" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I108" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J108" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K108">
         <v>65</v>
@@ -11044,7 +11056,7 @@
         <v>22.96551724</v>
       </c>
       <c r="W108" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X108">
         <v>0.036861</v>
@@ -11076,7 +11088,7 @@
         <v>25</v>
       </c>
       <c r="B109" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C109" s="2">
         <v>43905.38518045139</v>
@@ -11094,13 +11106,13 @@
         <v>2643</v>
       </c>
       <c r="H109" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I109" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J109" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K109">
         <v>78</v>
@@ -11127,7 +11139,7 @@
         <v>23.06896552</v>
       </c>
       <c r="W109" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X109">
         <v>0.003567</v>
@@ -11159,7 +11171,7 @@
         <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C110" s="2">
         <v>43905.38557278935</v>
@@ -11177,13 +11189,13 @@
         <v>2672</v>
       </c>
       <c r="H110" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I110" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J110" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K110">
         <v>102</v>
@@ -11210,7 +11222,7 @@
         <v>24.10344828</v>
       </c>
       <c r="W110" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X110">
         <v>0.035672</v>
@@ -11242,7 +11254,7 @@
         <v>25</v>
       </c>
       <c r="B111" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C111" s="2">
         <v>43905.38603423611</v>
@@ -11260,13 +11272,13 @@
         <v>2730</v>
       </c>
       <c r="H111" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I111" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J111" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K111">
         <v>84</v>
@@ -11293,7 +11305,7 @@
         <v>15.27586207</v>
       </c>
       <c r="W111" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X111">
         <v>-0.1522</v>
@@ -11325,7 +11337,7 @@
         <v>25</v>
       </c>
       <c r="B112" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C112" s="2">
         <v>43905.38641778935</v>
@@ -11343,13 +11355,13 @@
         <v>2759</v>
       </c>
       <c r="H112" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I112" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J112" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K112">
         <v>74</v>
@@ -11376,7 +11388,7 @@
         <v>16.4137931</v>
       </c>
       <c r="W112" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X112">
         <v>0.039239</v>
@@ -11408,7 +11420,7 @@
         <v>25</v>
       </c>
       <c r="B113" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C113" s="2">
         <v>43905.38679976852</v>
@@ -11426,13 +11438,13 @@
         <v>2788</v>
       </c>
       <c r="H113" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I113" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J113" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K113">
         <v>89</v>
@@ -11459,7 +11471,7 @@
         <v>19</v>
       </c>
       <c r="W113" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X113">
         <v>0.08918</v>
@@ -11491,7 +11503,7 @@
         <v>25</v>
       </c>
       <c r="B114" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C114" s="2">
         <v>43905.38757756945</v>
@@ -11509,13 +11521,13 @@
         <v>2846</v>
       </c>
       <c r="H114" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I114" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J114" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K114">
         <v>62</v>
@@ -11542,7 +11554,7 @@
         <v>14.53448276</v>
       </c>
       <c r="W114" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X114">
         <v>-0.076992</v>
@@ -11574,7 +11586,7 @@
         <v>25</v>
       </c>
       <c r="B115" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C115" s="2">
         <v>43905.38801688657</v>
@@ -11592,13 +11604,13 @@
         <v>2904</v>
       </c>
       <c r="H115" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I115" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J115" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K115">
         <v>60</v>
@@ -11625,7 +11637,7 @@
         <v>18.32758621</v>
       </c>
       <c r="W115" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X115">
         <v>0.065398</v>
@@ -11657,7 +11669,7 @@
         <v>25</v>
       </c>
       <c r="B116" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C116" s="2">
         <v>43905.38840190972</v>
@@ -11675,13 +11687,13 @@
         <v>2933</v>
       </c>
       <c r="H116" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I116" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J116" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K116">
         <v>60</v>
@@ -11708,7 +11720,7 @@
         <v>20.48275862</v>
       </c>
       <c r="W116" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X116">
         <v>0.07431599999999999</v>
@@ -11740,7 +11752,7 @@
         <v>25</v>
       </c>
       <c r="B117" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C117" s="2">
         <v>43905.38879309028</v>
@@ -11758,13 +11770,13 @@
         <v>2962</v>
       </c>
       <c r="H117" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I117" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J117" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K117">
         <v>65</v>
@@ -11791,7 +11803,7 @@
         <v>25.79310345</v>
       </c>
       <c r="W117" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X117">
         <v>0.183115</v>
@@ -11823,7 +11835,7 @@
         <v>25</v>
       </c>
       <c r="B118" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C118" s="2">
         <v>43905.38918696759</v>
@@ -11841,13 +11853,13 @@
         <v>2991</v>
       </c>
       <c r="H118" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I118" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J118" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K118">
         <v>75</v>
@@ -11874,7 +11886,7 @@
         <v>20.82758621</v>
       </c>
       <c r="W118" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X118">
         <v>-0.171225</v>
@@ -11906,7 +11918,7 @@
         <v>25</v>
       </c>
       <c r="B119" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C119" s="2">
         <v>43905.38957825232</v>
@@ -11924,13 +11936,13 @@
         <v>3020</v>
       </c>
       <c r="H119" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I119" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J119" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K119">
         <v>83</v>
@@ -11957,7 +11969,7 @@
         <v>18</v>
       </c>
       <c r="W119" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X119">
         <v>-0.09750300000000001</v>
@@ -11989,7 +12001,7 @@
         <v>25</v>
       </c>
       <c r="B120" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C120" s="2">
         <v>43905.39002297453</v>
@@ -12007,13 +12019,13 @@
         <v>3078</v>
       </c>
       <c r="H120" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I120" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J120" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K120">
         <v>79</v>
@@ -12040,7 +12052,7 @@
         <v>12.27586207</v>
       </c>
       <c r="W120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X120">
         <v>-0.098692</v>
@@ -12072,7 +12084,7 @@
         <v>25</v>
       </c>
       <c r="B121" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C121" s="2">
         <v>43905.3904039699</v>
@@ -12090,13 +12102,13 @@
         <v>3107</v>
       </c>
       <c r="H121" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I121" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J121" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K121">
         <v>72</v>
@@ -12123,7 +12135,7 @@
         <v>8.48275862</v>
       </c>
       <c r="W121" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X121">
         <v>-0.130797</v>
@@ -12155,7 +12167,7 @@
         <v>25</v>
       </c>
       <c r="B122" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C122" s="2">
         <v>43905.3907987963</v>
@@ -12173,13 +12185,13 @@
         <v>3136</v>
       </c>
       <c r="H122" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I122" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J122" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K122">
         <v>79</v>
@@ -12206,7 +12218,7 @@
         <v>12.44827586</v>
       </c>
       <c r="W122" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X122">
         <v>0.136742</v>
@@ -12238,7 +12250,7 @@
         <v>25</v>
       </c>
       <c r="B123" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C123" s="2">
         <v>43905.39118726852</v>
@@ -12256,13 +12268,13 @@
         <v>3165</v>
       </c>
       <c r="H123" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I123" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J123" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K123">
         <v>84</v>
@@ -12289,7 +12301,7 @@
         <v>16.62068966</v>
       </c>
       <c r="W123" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X123">
         <v>0.143876</v>
@@ -12321,7 +12333,7 @@
         <v>25</v>
       </c>
       <c r="B124" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C124" s="2">
         <v>43905.39156853009</v>
@@ -12339,13 +12351,13 @@
         <v>3194</v>
       </c>
       <c r="H124" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I124" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J124" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K124">
         <v>75</v>
@@ -12372,7 +12384,7 @@
         <v>17.10344828</v>
       </c>
       <c r="W124" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X124">
         <v>0.016647</v>
@@ -12404,7 +12416,7 @@
         <v>25</v>
       </c>
       <c r="B125" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C125" s="2">
         <v>43905.39196420139</v>
@@ -12422,13 +12434,13 @@
         <v>3223</v>
       </c>
       <c r="H125" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I125" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J125" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K125">
         <v>76</v>
@@ -12455,7 +12467,7 @@
         <v>21.37931034</v>
       </c>
       <c r="W125" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X125">
         <v>0.147444</v>
@@ -12487,7 +12499,7 @@
         <v>25</v>
       </c>
       <c r="B126" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C126" s="2">
         <v>43905.39203550926</v>
@@ -12505,13 +12517,13 @@
         <v>3252</v>
       </c>
       <c r="H126" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I126" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J126" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K126">
         <v>78</v>
@@ -12538,7 +12550,7 @@
         <v>22.17241379</v>
       </c>
       <c r="W126" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X126">
         <v>0.027348</v>
@@ -12570,7 +12582,7 @@
         <v>25</v>
       </c>
       <c r="B127" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C127" s="2">
         <v>43905.39242384259</v>
@@ -12588,13 +12600,13 @@
         <v>3281</v>
       </c>
       <c r="H127" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I127" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J127" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K127">
         <v>94</v>
@@ -12621,7 +12633,7 @@
         <v>20.37931034</v>
       </c>
       <c r="W127" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X127">
         <v>-0.061831</v>
@@ -12653,7 +12665,7 @@
         <v>25</v>
       </c>
       <c r="B128" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C128" s="2">
         <v>43905.39359981482</v>
@@ -12671,13 +12683,13 @@
         <v>3368</v>
       </c>
       <c r="H128" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I128" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J128" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K128">
         <v>90</v>
@@ -12704,7 +12716,7 @@
         <v>17.08045977</v>
       </c>
       <c r="W128" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X128">
         <v>-0.037918</v>
@@ -12736,7 +12748,7 @@
         <v>25</v>
       </c>
       <c r="B129" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C129" s="2">
         <v>43905.39406228009</v>
@@ -12754,13 +12766,13 @@
         <v>3426</v>
       </c>
       <c r="H129" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I129" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J129" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K129">
         <v>85</v>
@@ -12787,7 +12799,7 @@
         <v>12.56896552</v>
       </c>
       <c r="W129" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X129">
         <v>-0.07778400000000001</v>
@@ -12819,7 +12831,7 @@
         <v>25</v>
       </c>
       <c r="B130" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C130" s="2">
         <v>43905.39445508102</v>
@@ -12837,13 +12849,13 @@
         <v>3455</v>
       </c>
       <c r="H130" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I130" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J130" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K130">
         <v>81</v>
@@ -12870,7 +12882,7 @@
         <v>24.06896552</v>
       </c>
       <c r="W130" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X130">
         <v>0.396552</v>
@@ -12902,7 +12914,7 @@
         <v>25</v>
       </c>
       <c r="B131" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C131" s="2">
         <v>43905.39484420139</v>
@@ -12920,13 +12932,13 @@
         <v>3484</v>
       </c>
       <c r="H131" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I131" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J131" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K131">
         <v>88</v>
@@ -12953,7 +12965,7 @@
         <v>24.44827586</v>
       </c>
       <c r="W131" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X131">
         <v>0.01308</v>
@@ -12985,7 +12997,7 @@
         <v>25</v>
       </c>
       <c r="B132" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C132" s="2">
         <v>43905.39523104166</v>
@@ -13003,13 +13015,13 @@
         <v>3513</v>
       </c>
       <c r="H132" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I132" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J132" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K132">
         <v>92</v>
@@ -13036,7 +13048,7 @@
         <v>23.89655172</v>
       </c>
       <c r="W132" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X132">
         <v>-0.019025</v>
@@ -13068,7 +13080,7 @@
         <v>25</v>
       </c>
       <c r="B133" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C133" s="2">
         <v>43905.39608542824</v>
@@ -13086,13 +13098,13 @@
         <v>3600</v>
       </c>
       <c r="H133" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I133" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J133" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K133">
         <v>103</v>
@@ -13119,7 +13131,7 @@
         <v>26.24137931</v>
       </c>
       <c r="W133" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X133">
         <v>0.026952</v>
@@ -13151,7 +13163,7 @@
         <v>25</v>
       </c>
       <c r="B134" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C134" s="2">
         <v>43905.39647616898</v>
@@ -13169,13 +13181,13 @@
         <v>3629</v>
       </c>
       <c r="H134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I134" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J134" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K134">
         <v>104</v>
@@ -13202,7 +13214,7 @@
         <v>18.89655172</v>
       </c>
       <c r="W134" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X134">
         <v>-0.25327</v>
@@ -13234,7 +13246,7 @@
         <v>25</v>
       </c>
       <c r="B135" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C135" s="2">
         <v>43905.39686945602</v>
@@ -13252,13 +13264,13 @@
         <v>3658</v>
       </c>
       <c r="H135" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I135" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J135" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K135">
         <v>85</v>
@@ -13285,7 +13297,7 @@
         <v>11.44827586</v>
       </c>
       <c r="W135" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X135">
         <v>-0.256837</v>
@@ -13317,7 +13329,7 @@
         <v>25</v>
       </c>
       <c r="B136" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C136" s="2">
         <v>43905.39726204861</v>
@@ -13335,13 +13347,13 @@
         <v>3687</v>
       </c>
       <c r="H136" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I136" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J136" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K136">
         <v>85</v>
@@ -13368,7 +13380,7 @@
         <v>8.68965517</v>
       </c>
       <c r="W136" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X136">
         <v>-0.095125</v>
@@ -13400,7 +13412,7 @@
         <v>25</v>
       </c>
       <c r="B137" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C137" s="2">
         <v>43905.39810152777</v>
@@ -13418,13 +13430,13 @@
         <v>3774</v>
       </c>
       <c r="H137" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I137" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J137" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K137">
         <v>98</v>
@@ -13451,7 +13463,7 @@
         <v>13.91954023</v>
       </c>
       <c r="W137" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X137">
         <v>0.060114</v>
@@ -13483,7 +13495,7 @@
         <v>25</v>
       </c>
       <c r="B138" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C138" s="2">
         <v>43905.39889516203</v>
@@ -13501,13 +13513,13 @@
         <v>3832</v>
       </c>
       <c r="H138" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I138" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J138" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K138">
         <v>106</v>
@@ -13534,7 +13546,7 @@
         <v>20.31034483</v>
       </c>
       <c r="W138" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X138">
         <v>0.110186</v>
@@ -13566,7 +13578,7 @@
         <v>25</v>
       </c>
       <c r="B139" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C139" s="2">
         <v>43905.39929194444</v>
@@ -13584,13 +13596,13 @@
         <v>3861</v>
       </c>
       <c r="H139" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I139" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J139" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K139">
         <v>110</v>
@@ -13617,7 +13629,7 @@
         <v>18.34482759</v>
       </c>
       <c r="W139" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X139">
         <v>-0.067776</v>
@@ -13649,7 +13661,7 @@
         <v>25</v>
       </c>
       <c r="B140" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C140" s="2">
         <v>43905.39976372685</v>
@@ -13667,13 +13679,13 @@
         <v>3919</v>
       </c>
       <c r="H140" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I140" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J140" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K140">
         <v>99</v>
@@ -13700,7 +13712,7 @@
         <v>16.84482759</v>
       </c>
       <c r="W140" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X140">
         <v>-0.025862</v>
@@ -13732,7 +13744,7 @@
         <v>25</v>
       </c>
       <c r="B141" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C141" s="2">
         <v>43905.40017170139</v>
@@ -13750,13 +13762,13 @@
         <v>3948</v>
       </c>
       <c r="H141" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I141" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J141" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K141">
         <v>92</v>
@@ -13783,7 +13795,7 @@
         <v>8.275862070000001</v>
       </c>
       <c r="W141" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X141">
         <v>-0.295482</v>
@@ -13815,7 +13827,7 @@
         <v>25</v>
       </c>
       <c r="B142" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C142" s="2">
         <v>43905.40057579861</v>
@@ -13833,13 +13845,13 @@
         <v>3977</v>
       </c>
       <c r="H142" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I142" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J142" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K142">
         <v>88</v>
@@ -13866,7 +13878,7 @@
         <v>5.55172414</v>
       </c>
       <c r="W142" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X142">
         <v>-0.09393600000000001</v>
@@ -13898,7 +13910,7 @@
         <v>25</v>
       </c>
       <c r="B143" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C143" s="2">
         <v>43905.40097962963</v>
@@ -13916,13 +13928,13 @@
         <v>4006</v>
       </c>
       <c r="H143" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I143" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J143" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K143">
         <v>103</v>
@@ -13949,7 +13961,7 @@
         <v>10.72413793</v>
       </c>
       <c r="W143" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X143">
         <v>0.178359</v>
@@ -13981,7 +13993,7 @@
         <v>25</v>
       </c>
       <c r="B144" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C144" s="2">
         <v>43905.40145209491</v>
@@ -13999,13 +14011,13 @@
         <v>4064</v>
       </c>
       <c r="H144" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I144" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J144" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K144">
         <v>103</v>
@@ -14032,7 +14044,7 @@
         <v>16.81034483</v>
       </c>
       <c r="W144" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X144">
         <v>0.104935</v>
@@ -14064,7 +14076,7 @@
         <v>25</v>
       </c>
       <c r="B145" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C145" s="2">
         <v>43905.40186480324</v>
@@ -14082,13 +14094,13 @@
         <v>4093</v>
       </c>
       <c r="H145" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I145" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J145" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K145">
         <v>97</v>
@@ -14115,7 +14127,7 @@
         <v>15.62068966</v>
       </c>
       <c r="W145" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X145">
         <v>-0.041023</v>
@@ -14147,7 +14159,7 @@
         <v>25</v>
       </c>
       <c r="B146" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C146" s="2">
         <v>43905.40227127315</v>
@@ -14165,13 +14177,13 @@
         <v>4122</v>
       </c>
       <c r="H146" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I146" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J146" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K146">
         <v>96</v>
@@ -14198,7 +14210,7 @@
         <v>16.72413793</v>
       </c>
       <c r="W146" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X146">
         <v>0.03805</v>
@@ -14230,7 +14242,7 @@
         <v>25</v>
       </c>
       <c r="B147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C147" s="2">
         <v>43905.40267277777</v>
@@ -14248,13 +14260,13 @@
         <v>4151</v>
       </c>
       <c r="H147" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I147" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J147" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K147">
         <v>95</v>
@@ -14281,7 +14293,7 @@
         <v>17.31034483</v>
       </c>
       <c r="W147" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X147">
         <v>0.020214</v>
@@ -14313,7 +14325,7 @@
         <v>25</v>
       </c>
       <c r="B148" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C148" s="2">
         <v>43905.40316255787</v>
@@ -14331,13 +14343,13 @@
         <v>4209</v>
       </c>
       <c r="H148" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I148" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J148" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K148">
         <v>92</v>
@@ -14364,7 +14376,7 @@
         <v>17.94827586</v>
       </c>
       <c r="W148" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X148">
         <v>0.010999</v>
@@ -14396,7 +14408,7 @@
         <v>25</v>
       </c>
       <c r="B149" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C149" s="2">
         <v>43905.40357260417</v>
@@ -14414,13 +14426,13 @@
         <v>4238</v>
       </c>
       <c r="H149" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I149" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J149" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K149">
         <v>95</v>
@@ -14447,7 +14459,7 @@
         <v>15.37931034</v>
       </c>
       <c r="W149" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X149">
         <v>-0.088585</v>
@@ -14479,7 +14491,7 @@
         <v>25</v>
       </c>
       <c r="B150" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C150" s="2">
         <v>43905.40397891204</v>
@@ -14497,13 +14509,13 @@
         <v>4267</v>
       </c>
       <c r="H150" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I150" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J150" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K150">
         <v>90</v>
@@ -14530,7 +14542,7 @@
         <v>15.27586207</v>
       </c>
       <c r="W150" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X150">
         <v>-0.003567</v>
@@ -14562,7 +14574,7 @@
         <v>25</v>
       </c>
       <c r="B151" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C151" s="2">
         <v>43905.40446133102</v>
@@ -14580,13 +14592,13 @@
         <v>4325</v>
       </c>
       <c r="H151" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I151" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J151" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K151">
         <v>89</v>
@@ -14613,7 +14625,7 @@
         <v>12.15517241</v>
       </c>
       <c r="W151" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X151">
         <v>-0.053805</v>
@@ -14645,7 +14657,7 @@
         <v>25</v>
       </c>
       <c r="B152" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C152" s="2">
         <v>43905.40485790509</v>
@@ -14663,13 +14675,13 @@
         <v>4354</v>
       </c>
       <c r="H152" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I152" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J152" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K152">
         <v>87</v>
@@ -14696,7 +14708,7 @@
         <v>11.79310345</v>
       </c>
       <c r="W152" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X152">
         <v>-0.012485</v>
@@ -14728,7 +14740,7 @@
         <v>25</v>
       </c>
       <c r="B153" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C153" s="2">
         <v>43905.40527519676</v>
@@ -14746,13 +14758,13 @@
         <v>4383</v>
       </c>
       <c r="H153" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I153" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J153" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K153">
         <v>79</v>
@@ -14779,7 +14791,7 @@
         <v>17.86206897</v>
       </c>
       <c r="W153" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X153">
         <v>0.209275</v>
@@ -14811,7 +14823,7 @@
         <v>25</v>
       </c>
       <c r="B154" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C154" s="2">
         <v>43905.40568210648</v>
@@ -14829,13 +14841,13 @@
         <v>4412</v>
       </c>
       <c r="H154" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I154" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J154" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K154">
         <v>76</v>
@@ -14862,7 +14874,7 @@
         <v>19.79310345</v>
       </c>
       <c r="W154" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X154">
         <v>0.06658699999999999</v>
@@ -14894,7 +14906,7 @@
         <v>25</v>
       </c>
       <c r="B155" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C155" s="2">
         <v>43905.40616476852</v>
@@ -14912,13 +14924,13 @@
         <v>4470</v>
       </c>
       <c r="H155" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I155" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J155" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K155">
         <v>88</v>
@@ -14945,7 +14957,7 @@
         <v>21.72413793</v>
       </c>
       <c r="W155" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X155">
         <v>0.033294</v>
@@ -14979,10 +14991,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE71"/>
+  <dimension ref="A1:AF71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -15076,13 +15088,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2">
         <v>43905.40656033565</v>
@@ -15100,13 +15115,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K2">
         <v>78</v>
@@ -15133,7 +15148,7 @@
         <v>-22.17241379</v>
       </c>
       <c r="W2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="Y2">
         <v>-22.172414</v>
@@ -15142,12 +15157,12 @@
         <v>-22.187358</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2">
         <v>43905.40696612268</v>
@@ -15165,13 +15180,13 @@
         <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K3">
         <v>89</v>
@@ -15198,7 +15213,7 @@
         <v>-101.5862069</v>
       </c>
       <c r="W3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X3">
         <v>-2.738407</v>
@@ -15219,12 +15234,12 @@
         <v>-101.322496</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2">
         <v>43905.40736842593</v>
@@ -15242,13 +15257,13 @@
         <v>58</v>
       </c>
       <c r="H4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K4">
         <v>119</v>
@@ -15275,7 +15290,7 @@
         <v>-90.41379310000001</v>
       </c>
       <c r="W4" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X4">
         <v>0.385256</v>
@@ -15302,12 +15317,12 @@
         <v>-91.32858</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" s="2">
         <v>43905.40785921297</v>
@@ -15325,13 +15340,13 @@
         <v>116</v>
       </c>
       <c r="H5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I5" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J5" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K5">
         <v>117</v>
@@ -15358,7 +15373,7 @@
         <v>-82.15517241000001</v>
       </c>
       <c r="W5" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X5">
         <v>0.14239</v>
@@ -15385,12 +15400,12 @@
         <v>-78.37444000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2">
         <v>43905.40825150463</v>
@@ -15408,13 +15423,13 @@
         <v>145</v>
       </c>
       <c r="H6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K6">
         <v>108</v>
@@ -15441,7 +15456,7 @@
         <v>-73.75862069</v>
       </c>
       <c r="W6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X6">
         <v>0.289536</v>
@@ -15468,12 +15483,12 @@
         <v>-76.682529</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2">
         <v>43905.40865800926</v>
@@ -15491,13 +15506,13 @@
         <v>174</v>
       </c>
       <c r="H7" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J7" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K7">
         <v>73</v>
@@ -15524,7 +15539,7 @@
         <v>-71.27586207</v>
       </c>
       <c r="W7" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X7">
         <v>0.08561199999999999</v>
@@ -15551,12 +15566,12 @@
         <v>-74.001594</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2">
         <v>43905.40954530093</v>
@@ -15574,13 +15589,13 @@
         <v>261</v>
       </c>
       <c r="H8" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I8" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="K8">
         <v>87</v>
@@ -15607,7 +15622,7 @@
         <v>-68.94252874</v>
       </c>
       <c r="W8" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X8">
         <v>0.02682</v>
@@ -15634,12 +15649,12 @@
         <v>-60.586489</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" s="2">
         <v>43905.40993851852</v>
@@ -15657,13 +15672,13 @@
         <v>290</v>
       </c>
       <c r="H9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J9" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K9">
         <v>84</v>
@@ -15690,7 +15705,7 @@
         <v>-56.79310345</v>
       </c>
       <c r="W9" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X9">
         <v>0.418946</v>
@@ -15717,12 +15732,12 @@
         <v>-57.268818</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2">
         <v>43905.41034855324</v>
@@ -15740,13 +15755,13 @@
         <v>319</v>
       </c>
       <c r="H10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J10" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K10">
         <v>93</v>
@@ -15773,7 +15788,7 @@
         <v>-53.51724138</v>
       </c>
       <c r="W10" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X10">
         <v>0.112961</v>
@@ -15800,12 +15815,12 @@
         <v>-54.714515</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" s="2">
         <v>43905.41074886574</v>
@@ -15823,13 +15838,13 @@
         <v>348</v>
       </c>
       <c r="H11" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I11" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J11" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K11">
         <v>53</v>
@@ -15856,7 +15871,7 @@
         <v>-46.96551724</v>
       </c>
       <c r="W11" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X11">
         <v>0.225922</v>
@@ -15883,12 +15898,12 @@
         <v>-52.898122</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" s="2">
         <v>43905.41122502315</v>
@@ -15906,13 +15921,13 @@
         <v>406</v>
       </c>
       <c r="H12" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I12" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J12" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K12">
         <v>60</v>
@@ -15939,7 +15954,7 @@
         <v>-45.87931034</v>
       </c>
       <c r="W12" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X12">
         <v>0.018728</v>
@@ -15966,12 +15981,12 @@
         <v>-50.087159</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" s="2">
         <v>43905.41162112269</v>
@@ -15989,13 +16004,13 @@
         <v>435</v>
       </c>
       <c r="H13" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I13" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J13" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="K13">
         <v>65</v>
@@ -16022,7 +16037,7 @@
         <v>-48.10344828</v>
       </c>
       <c r="W13" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X13">
         <v>-0.076694</v>
@@ -16049,12 +16064,12 @@
         <v>-48.741655</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="2">
         <v>43905.41203418982</v>
@@ -16072,13 +16087,13 @@
         <v>464</v>
       </c>
       <c r="H14" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I14" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="J14" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K14">
         <v>83</v>
@@ -16105,7 +16120,7 @@
         <v>-50.79310345</v>
       </c>
       <c r="W14" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X14">
         <v>-0.092747</v>
@@ -16132,12 +16147,12 @@
         <v>-47.243447</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="2">
         <v>43905.41243891204</v>
@@ -16155,13 +16170,13 @@
         <v>493</v>
       </c>
       <c r="H15" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J15" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="K15">
         <v>92</v>
@@ -16188,7 +16203,7 @@
         <v>-49.79310345</v>
       </c>
       <c r="W15" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X15">
         <v>0.034483</v>
@@ -16215,12 +16230,12 @@
         <v>-45.618117</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" s="2">
         <v>43905.4125115162</v>
@@ -16238,13 +16253,13 @@
         <v>522</v>
       </c>
       <c r="H16" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I16" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J16" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K16">
         <v>57</v>
@@ -16271,7 +16286,7 @@
         <v>-47.17241379</v>
       </c>
       <c r="W16" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X16">
         <v>0.090369</v>
@@ -16303,7 +16318,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" s="2">
         <v>43905.41291292824</v>
@@ -16321,13 +16336,13 @@
         <v>551</v>
       </c>
       <c r="H17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I17" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J17" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K17">
         <v>80</v>
@@ -16354,7 +16369,7 @@
         <v>-42.55172414</v>
       </c>
       <c r="W17" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X17">
         <v>0.159334</v>
@@ -16386,7 +16401,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18" s="2">
         <v>43905.41330755787</v>
@@ -16404,13 +16419,13 @@
         <v>580</v>
       </c>
       <c r="H18" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I18" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J18" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K18">
         <v>84</v>
@@ -16437,7 +16452,7 @@
         <v>-43.10344828</v>
       </c>
       <c r="W18" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X18">
         <v>-0.019025</v>
@@ -16469,7 +16484,7 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="2">
         <v>43905.4137133912</v>
@@ -16487,13 +16502,13 @@
         <v>609</v>
       </c>
       <c r="H19" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I19" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J19" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K19">
         <v>74</v>
@@ -16520,7 +16535,7 @@
         <v>-37</v>
       </c>
       <c r="W19" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X19">
         <v>0.210464</v>
@@ -16552,7 +16567,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="2">
         <v>43905.41410821759</v>
@@ -16570,13 +16585,13 @@
         <v>638</v>
       </c>
       <c r="H20" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I20" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J20" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K20">
         <v>89</v>
@@ -16603,7 +16618,7 @@
         <v>-35.86206897</v>
       </c>
       <c r="W20" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X20">
         <v>0.039239</v>
@@ -16635,7 +16650,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="2">
         <v>43905.41418798611</v>
@@ -16653,13 +16668,13 @@
         <v>667</v>
       </c>
       <c r="H21" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I21" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J21" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K21">
         <v>86</v>
@@ -16686,7 +16701,7 @@
         <v>-34.51724138</v>
       </c>
       <c r="W21" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X21">
         <v>0.046373</v>
@@ -16718,7 +16733,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C22" s="2">
         <v>43905.41459003472</v>
@@ -16736,13 +16751,13 @@
         <v>696</v>
       </c>
       <c r="H22" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I22" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J22" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K22">
         <v>80</v>
@@ -16769,7 +16784,7 @@
         <v>-31.68965517</v>
       </c>
       <c r="W22" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X22">
         <v>0.09750300000000001</v>
@@ -16801,7 +16816,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C23" s="2">
         <v>43905.41498318287</v>
@@ -16819,13 +16834,13 @@
         <v>725</v>
       </c>
       <c r="H23" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I23" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J23" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K23">
         <v>71</v>
@@ -16852,7 +16867,7 @@
         <v>-29.51724138</v>
       </c>
       <c r="W23" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X23">
         <v>0.07491100000000001</v>
@@ -16884,7 +16899,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24" s="2">
         <v>43905.41538748843</v>
@@ -16902,13 +16917,13 @@
         <v>754</v>
       </c>
       <c r="H24" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I24" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J24" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="K24">
         <v>69</v>
@@ -16935,7 +16950,7 @@
         <v>-30.89655172</v>
       </c>
       <c r="W24" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X24">
         <v>-0.047562</v>
@@ -16967,7 +16982,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="2">
         <v>43905.41578619213</v>
@@ -16985,13 +17000,13 @@
         <v>783</v>
       </c>
       <c r="H25" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I25" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J25" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K25">
         <v>76</v>
@@ -17018,7 +17033,7 @@
         <v>-32.79310345</v>
       </c>
       <c r="W25" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X25">
         <v>-0.065398</v>
@@ -17050,7 +17065,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" s="2">
         <v>43905.41586673611</v>
@@ -17068,13 +17083,13 @@
         <v>812</v>
       </c>
       <c r="H26" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I26" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="J26" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K26">
         <v>72</v>
@@ -17101,7 +17116,7 @@
         <v>-34.17241379</v>
       </c>
       <c r="W26" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X26">
         <v>-0.047562</v>
@@ -17133,7 +17148,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="2">
         <v>43905.41627064815</v>
@@ -17151,13 +17166,13 @@
         <v>841</v>
       </c>
       <c r="H27" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I27" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J27" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="K27">
         <v>65</v>
@@ -17184,7 +17199,7 @@
         <v>-34.96551724</v>
       </c>
       <c r="W27" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X27">
         <v>-0.027348</v>
@@ -17216,7 +17231,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" s="2">
         <v>43905.41666415509</v>
@@ -17234,13 +17249,13 @@
         <v>870</v>
       </c>
       <c r="H28" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I28" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J28" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K28">
         <v>61</v>
@@ -17267,7 +17282,7 @@
         <v>-34.17241379</v>
       </c>
       <c r="W28" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X28">
         <v>0.027348</v>
@@ -17299,7 +17314,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" s="2">
         <v>43905.41711885417</v>
@@ -17317,13 +17332,13 @@
         <v>903</v>
       </c>
       <c r="H29" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I29" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J29" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K29">
         <v>53</v>
@@ -17350,7 +17365,7 @@
         <v>-33.81818182</v>
       </c>
       <c r="W29" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X29">
         <v>0.010734</v>
@@ -17382,7 +17397,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" s="2">
         <v>43905.41760005787</v>
@@ -17400,13 +17415,13 @@
         <v>961</v>
       </c>
       <c r="H30" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I30" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J30" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K30">
         <v>65</v>
@@ -17433,7 +17448,7 @@
         <v>-27.94827586</v>
       </c>
       <c r="W30" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X30">
         <v>0.101205</v>
@@ -17465,7 +17480,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C31" s="2">
         <v>43905.41798528935</v>
@@ -17483,13 +17498,13 @@
         <v>990</v>
       </c>
       <c r="H31" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I31" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J31" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="K31">
         <v>62</v>
@@ -17516,7 +17531,7 @@
         <v>-25.55172414</v>
       </c>
       <c r="W31" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X31">
         <v>0.08264000000000001</v>
@@ -17548,7 +17563,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="2">
         <v>43905.41839347222</v>
@@ -17566,13 +17581,13 @@
         <v>1019</v>
       </c>
       <c r="H32" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I32" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J32" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K32">
         <v>65</v>
@@ -17599,7 +17614,7 @@
         <v>-25.79310345</v>
       </c>
       <c r="W32" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X32">
         <v>-0.008323000000000001</v>
@@ -17631,7 +17646,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" s="2">
         <v>43905.41879380787</v>
@@ -17649,13 +17664,13 @@
         <v>1048</v>
       </c>
       <c r="H33" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I33" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J33" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K33">
         <v>64</v>
@@ -17682,7 +17697,7 @@
         <v>-25.93103448</v>
       </c>
       <c r="W33" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X33">
         <v>-0.004756</v>
@@ -17714,7 +17729,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C34" s="2">
         <v>43905.41919268519</v>
@@ -17732,13 +17747,13 @@
         <v>1077</v>
       </c>
       <c r="H34" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I34" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J34" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K34">
         <v>58</v>
@@ -17765,7 +17780,7 @@
         <v>-26.34482759</v>
       </c>
       <c r="W34" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X34">
         <v>-0.014269</v>
@@ -17797,7 +17812,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C35" s="2">
         <v>43905.41965954861</v>
@@ -17815,13 +17830,13 @@
         <v>1135</v>
       </c>
       <c r="H35" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I35" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J35" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K35">
         <v>60</v>
@@ -17848,7 +17863,7 @@
         <v>-25.5862069</v>
       </c>
       <c r="W35" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X35">
         <v>0.01308</v>
@@ -17880,7 +17895,7 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C36" s="2">
         <v>43905.4200671875</v>
@@ -17898,13 +17913,13 @@
         <v>1164</v>
       </c>
       <c r="H36" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I36" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J36" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K36">
         <v>70</v>
@@ -17931,7 +17946,7 @@
         <v>-25.89655172</v>
       </c>
       <c r="W36" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X36">
         <v>-0.010702</v>
@@ -17963,7 +17978,7 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C37" s="2">
         <v>43905.42046076389</v>
@@ -17981,13 +17996,13 @@
         <v>1193</v>
       </c>
       <c r="H37" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I37" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J37" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="K37">
         <v>57</v>
@@ -18014,7 +18029,7 @@
         <v>-25.79310345</v>
       </c>
       <c r="W37" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X37">
         <v>0.003567</v>
@@ -18046,7 +18061,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C38" s="2">
         <v>43905.42085435185</v>
@@ -18064,13 +18079,13 @@
         <v>1222</v>
       </c>
       <c r="H38" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I38" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J38" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K38">
         <v>63</v>
@@ -18097,7 +18112,7 @@
         <v>-25</v>
       </c>
       <c r="W38" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X38">
         <v>0.027348</v>
@@ -18129,7 +18144,7 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C39" s="2">
         <v>43905.42130972222</v>
@@ -18147,13 +18162,13 @@
         <v>1280</v>
       </c>
       <c r="H39" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I39" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J39" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K39">
         <v>71</v>
@@ -18180,7 +18195,7 @@
         <v>-24.89655172</v>
       </c>
       <c r="W39" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X39">
         <v>0.001784</v>
@@ -18212,7 +18227,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C40" s="2">
         <v>43905.42170667824</v>
@@ -18230,13 +18245,13 @@
         <v>1309</v>
       </c>
       <c r="H40" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I40" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J40" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="K40">
         <v>57</v>
@@ -18263,7 +18278,7 @@
         <v>-23.86206897</v>
       </c>
       <c r="W40" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X40">
         <v>0.035672</v>
@@ -18295,7 +18310,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C41" s="2">
         <v>43905.42209358796</v>
@@ -18313,13 +18328,13 @@
         <v>1338</v>
       </c>
       <c r="H41" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I41" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J41" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="K41">
         <v>77</v>
@@ -18346,7 +18361,7 @@
         <v>-22.86206897</v>
       </c>
       <c r="W41" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X41">
         <v>0.034483</v>
@@ -18378,7 +18393,7 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C42" s="2">
         <v>43905.42249329861</v>
@@ -18396,13 +18411,13 @@
         <v>1367</v>
       </c>
       <c r="H42" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I42" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J42" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K42">
         <v>80</v>
@@ -18429,7 +18444,7 @@
         <v>-22.51724138</v>
       </c>
       <c r="W42" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X42">
         <v>0.011891</v>
@@ -18461,7 +18476,7 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C43" s="2">
         <v>43905.42288127315</v>
@@ -18479,13 +18494,13 @@
         <v>1396</v>
       </c>
       <c r="H43" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I43" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J43" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K43">
         <v>79</v>
@@ -18512,7 +18527,7 @@
         <v>-21.72413793</v>
       </c>
       <c r="W43" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X43">
         <v>0.027348</v>
@@ -18544,7 +18559,7 @@
         <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C44" s="2">
         <v>43905.42333550926</v>
@@ -18562,13 +18577,13 @@
         <v>1454</v>
       </c>
       <c r="H44" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I44" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J44" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K44">
         <v>90</v>
@@ -18595,7 +18610,7 @@
         <v>-21.27586207</v>
       </c>
       <c r="W44" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X44">
         <v>0.007729</v>
@@ -18627,7 +18642,7 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C45" s="2">
         <v>43905.42372643518</v>
@@ -18645,13 +18660,13 @@
         <v>1483</v>
       </c>
       <c r="H45" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I45" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J45" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="K45">
         <v>66</v>
@@ -18678,7 +18693,7 @@
         <v>-21.48275862</v>
       </c>
       <c r="W45" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X45">
         <v>-0.007134</v>
@@ -18710,7 +18725,7 @@
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C46" s="2">
         <v>43905.42411983796</v>
@@ -18728,13 +18743,13 @@
         <v>1512</v>
       </c>
       <c r="H46" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I46" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J46" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="K46">
         <v>77</v>
@@ -18761,7 +18776,7 @@
         <v>-21.06896552</v>
       </c>
       <c r="W46" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X46">
         <v>0.014269</v>
@@ -18793,7 +18808,7 @@
         <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C47" s="2">
         <v>43905.4245116551</v>
@@ -18811,13 +18826,13 @@
         <v>1541</v>
       </c>
       <c r="H47" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I47" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J47" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K47">
         <v>66</v>
@@ -18844,7 +18859,7 @@
         <v>-21.13793103</v>
       </c>
       <c r="W47" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X47">
         <v>-0.002378</v>
@@ -18876,7 +18891,7 @@
         <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C48" s="2">
         <v>43905.4248938426</v>
@@ -18894,13 +18909,13 @@
         <v>1570</v>
       </c>
       <c r="H48" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I48" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J48" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K48">
         <v>81</v>
@@ -18927,7 +18942,7 @@
         <v>-21.51724138</v>
       </c>
       <c r="W48" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X48">
         <v>-0.01308</v>
@@ -18959,7 +18974,7 @@
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C49" s="2">
         <v>43905.42497346065</v>
@@ -18977,13 +18992,13 @@
         <v>1599</v>
       </c>
       <c r="H49" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I49" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J49" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K49">
         <v>65</v>
@@ -19010,7 +19025,7 @@
         <v>-21.48275862</v>
       </c>
       <c r="W49" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X49">
         <v>0.001189</v>
@@ -19042,7 +19057,7 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C50" s="2">
         <v>43905.42536865741</v>
@@ -19060,13 +19075,13 @@
         <v>1628</v>
       </c>
       <c r="H50" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I50" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="J50" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K50">
         <v>72</v>
@@ -19093,7 +19108,7 @@
         <v>-21.51724138</v>
       </c>
       <c r="W50" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X50">
         <v>-0.001189</v>
@@ -19125,7 +19140,7 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C51" s="2">
         <v>43905.4257625</v>
@@ -19143,13 +19158,13 @@
         <v>1657</v>
       </c>
       <c r="H51" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I51" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J51" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K51">
         <v>68</v>
@@ -19176,7 +19191,7 @@
         <v>-21.72413793</v>
       </c>
       <c r="W51" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X51">
         <v>-0.007134</v>
@@ -19208,7 +19223,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C52" s="2">
         <v>43905.42615916667</v>
@@ -19226,13 +19241,13 @@
         <v>1686</v>
       </c>
       <c r="H52" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I52" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J52" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K52">
         <v>78</v>
@@ -19259,7 +19274,7 @@
         <v>-21.5862069</v>
       </c>
       <c r="W52" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X52">
         <v>0.004756</v>
@@ -19291,7 +19306,7 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C53" s="2">
         <v>43905.42701133102</v>
@@ -19309,13 +19324,13 @@
         <v>1773</v>
       </c>
       <c r="H53" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I53" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J53" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K53">
         <v>66</v>
@@ -19342,7 +19357,7 @@
         <v>-21.01149425</v>
       </c>
       <c r="W53" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X53">
         <v>0.006606</v>
@@ -19374,7 +19389,7 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C54" s="2">
         <v>43905.42740899305</v>
@@ -19392,13 +19407,13 @@
         <v>1802</v>
       </c>
       <c r="H54" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I54" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J54" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K54">
         <v>70</v>
@@ -19425,7 +19440,7 @@
         <v>-20.68965517</v>
       </c>
       <c r="W54" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X54">
         <v>0.011098</v>
@@ -19457,7 +19472,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C55" s="2">
         <v>43905.42778587963</v>
@@ -19475,13 +19490,13 @@
         <v>1831</v>
       </c>
       <c r="H55" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I55" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J55" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="K55">
         <v>41</v>
@@ -19508,7 +19523,7 @@
         <v>-20.27586207</v>
       </c>
       <c r="W55" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X55">
         <v>0.014269</v>
@@ -19540,7 +19555,7 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C56" s="2">
         <v>43905.4281658912</v>
@@ -19558,13 +19573,13 @@
         <v>1860</v>
       </c>
       <c r="H56" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I56" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="J56" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K56">
         <v>53</v>
@@ -19591,7 +19606,7 @@
         <v>-19</v>
       </c>
       <c r="W56" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X56">
         <v>0.043995</v>
@@ -19623,7 +19638,7 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C57" s="2">
         <v>43905.42855125</v>
@@ -19641,13 +19656,13 @@
         <v>1889</v>
       </c>
       <c r="H57" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I57" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J57" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K57">
         <v>69</v>
@@ -19674,7 +19689,7 @@
         <v>-18.79310345</v>
       </c>
       <c r="W57" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X57">
         <v>0.007134</v>
@@ -19706,7 +19721,7 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C58" s="2">
         <v>43905.42893336806</v>
@@ -19724,13 +19739,13 @@
         <v>1918</v>
       </c>
       <c r="H58" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I58" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J58" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K58">
         <v>98</v>
@@ -19757,7 +19772,7 @@
         <v>-18.31034483</v>
       </c>
       <c r="W58" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X58">
         <v>0.016647</v>
@@ -19789,7 +19804,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C59" s="2">
         <v>43905.42937478009</v>
@@ -19807,13 +19822,13 @@
         <v>1976</v>
       </c>
       <c r="H59" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I59" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J59" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="K59">
         <v>64</v>
@@ -19840,7 +19855,7 @@
         <v>-18.39655172</v>
       </c>
       <c r="W59" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X59">
         <v>-0.001486</v>
@@ -19872,7 +19887,7 @@
         <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C60" s="2">
         <v>43905.42975957176</v>
@@ -19890,13 +19905,13 @@
         <v>2005</v>
       </c>
       <c r="H60" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I60" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J60" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K60">
         <v>93</v>
@@ -19923,7 +19938,7 @@
         <v>-17.75862069</v>
       </c>
       <c r="W60" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X60">
         <v>0.021998</v>
@@ -19955,7 +19970,7 @@
         <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C61" s="2">
         <v>43905.43052959491</v>
@@ -19973,13 +19988,13 @@
         <v>2063</v>
       </c>
       <c r="H61" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I61" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J61" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K61">
         <v>101</v>
@@ -20006,7 +20021,7 @@
         <v>-18.5</v>
       </c>
       <c r="W61" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X61">
         <v>-0.012782</v>
@@ -20038,7 +20053,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C62" s="2">
         <v>43905.43129665509</v>
@@ -20056,13 +20071,13 @@
         <v>2121</v>
       </c>
       <c r="H62" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I62" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="J62" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K62">
         <v>177</v>
@@ -20089,7 +20104,7 @@
         <v>-17.48275862</v>
       </c>
       <c r="W62" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X62">
         <v>0.017539</v>
@@ -20121,7 +20136,7 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C63" s="2">
         <v>43905.43211053241</v>
@@ -20139,13 +20154,13 @@
         <v>2208</v>
       </c>
       <c r="H63" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I63" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J63" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K63">
         <v>202</v>
@@ -20172,7 +20187,7 @@
         <v>-17.98850575</v>
       </c>
       <c r="W63" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X63">
         <v>-0.005813</v>
@@ -20204,7 +20219,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64" s="2">
         <v>43905.4324965162</v>
@@ -20222,13 +20237,13 @@
         <v>2237</v>
       </c>
       <c r="H64" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I64" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="J64" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="K64">
         <v>214</v>
@@ -20255,7 +20270,7 @@
         <v>-18.20689655</v>
       </c>
       <c r="W64" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X64">
         <v>-0.007531</v>
@@ -20287,7 +20302,7 @@
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C65" s="2">
         <v>43905.43288127315</v>
@@ -20305,13 +20320,13 @@
         <v>2266</v>
       </c>
       <c r="H65" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I65" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J65" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="K65">
         <v>160</v>
@@ -20338,7 +20353,7 @@
         <v>-17.31034483</v>
       </c>
       <c r="W65" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X65">
         <v>0.030916</v>
@@ -20370,7 +20385,7 @@
         <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C66" s="2">
         <v>43905.43325335648</v>
@@ -20388,13 +20403,13 @@
         <v>2295</v>
       </c>
       <c r="H66" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I66" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J66" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="K66">
         <v>161</v>
@@ -20421,7 +20436,7 @@
         <v>-18.20689655</v>
       </c>
       <c r="W66" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X66">
         <v>-0.030916</v>
@@ -20453,7 +20468,7 @@
         <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C67" s="2">
         <v>43905.43409900463</v>
@@ -20471,13 +20486,13 @@
         <v>2382</v>
       </c>
       <c r="H67" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I67" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J67" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="K67">
         <v>66</v>
@@ -20504,7 +20519,7 @@
         <v>-17.8045977</v>
       </c>
       <c r="W67" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X67">
         <v>0.004624</v>
@@ -20536,7 +20551,7 @@
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C68" s="2">
         <v>43905.43447773148</v>
@@ -20554,13 +20569,13 @@
         <v>2411</v>
       </c>
       <c r="H68" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I68" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="J68" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="K68">
         <v>9</v>
@@ -20587,7 +20602,7 @@
         <v>-16.86206897</v>
       </c>
       <c r="W68" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X68">
         <v>0.032501</v>
@@ -20619,7 +20634,7 @@
         <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C69" s="2">
         <v>43905.43486143518</v>
@@ -20637,13 +20652,13 @@
         <v>2440</v>
       </c>
       <c r="H69" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I69" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J69" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="K69">
         <v>13</v>
@@ -20670,7 +20685,7 @@
         <v>-17.65517241</v>
       </c>
       <c r="W69" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X69">
         <v>-0.027348</v>
@@ -20702,7 +20717,7 @@
         <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C70" s="2">
         <v>43905.43563552084</v>
@@ -20720,13 +20735,13 @@
         <v>2498</v>
       </c>
       <c r="H70" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I70" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J70" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K70">
         <v>8</v>
@@ -20753,7 +20768,7 @@
         <v>-16.9137931</v>
       </c>
       <c r="W70" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X70">
         <v>0.012782</v>
@@ -20785,7 +20800,7 @@
         <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C71" s="2">
         <v>43905.4360971875</v>
@@ -20803,13 +20818,13 @@
         <v>2556</v>
       </c>
       <c r="H71" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I71" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J71" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K71">
         <v>356</v>
@@ -20836,7 +20851,7 @@
         <v>-9.448275860000001</v>
       </c>
       <c r="W71" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X71">
         <v>0.128716</v>

--- a/www/flightdata/xlsx/eoss-297.xlsx
+++ b/www/flightdata/xlsx/eoss-297.xlsx
@@ -2193,7 +2193,7 @@
         <v>26009.19</v>
       </c>
       <c r="I2">
-        <v>386</v>
+        <v>229</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
